--- a/research/traditional_assets/database/data/ivory_coast/ivory_coast_transportation.xlsx
+++ b/research/traditional_assets/database/data/ivory_coast/ivory_coast_transportation.xlsx
@@ -641,10 +641,10 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.140001177506065</v>
+        <v>0.1196364065731787</v>
       </c>
       <c r="AB2">
-        <v>0.140001177506065</v>
+        <v>0.1196364065731787</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -745,10 +745,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.140001177506065</v>
+        <v>0.1196364065731787</v>
       </c>
       <c r="AB3">
-        <v>0.140001177506065</v>
+        <v>0.1196364065731787</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -788,7 +788,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ2"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -814,197 +814,237 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>actual_debt_capital</t>
+          <t>current_interest_coverage</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>optimal_debt_capital</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>actual_equity_value</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>optimal_equity_value</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>actual_enterprise_value</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>optimal_enterprise_value</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>actual_debt</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>optimal_debt</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>actual_cost_capital</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>optimal_cost_capital</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>actual_cost_debt_after_tax</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>optimal_cost_debt_after_tax</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>actual_debt_rating</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>optimal_debt_rating</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>actual_cost_equity</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>optimal_cost_equity</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>actual_beta</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>optimal_beta</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>coverage_ratio</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>coverage_error</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>country_default_spread</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>risk_free</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>market_capitalization</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>estimated_risk_premium</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>estimated_cost_debt_pre_tax</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>marginal_tax_rate</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>deductions_max_percentage</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>deductions_method</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>adjusted_ebitda</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>adjusted_depreciation</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>reported_capital_spending</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>adjusted_debt</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>estimated_mv_debt</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>reported_interest_expense</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>reported_bv_debt</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>reported_cash</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>flag_bankruptcy</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>flag_refinanced</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
         </is>
       </c>
     </row>
@@ -1030,122 +1070,141 @@
         </is>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>-6.3905325443787</v>
       </c>
       <c r="F2">
+        <v>-36.5316079590197</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
         <v>0.01</v>
       </c>
-      <c r="G2">
-        <v>123.7</v>
-      </c>
-      <c r="H2">
-        <v>91.9916892465711</v>
-      </c>
-      <c r="I2">
-        <v>123.7</v>
-      </c>
-      <c r="J2">
-        <v>93.22868924657109</v>
-      </c>
       <c r="K2">
-        <v>0</v>
+        <v>123.8</v>
       </c>
       <c r="L2">
-        <v>1.237</v>
+        <v>88.0923789372744</v>
       </c>
       <c r="M2">
-        <v>0.140001177506065</v>
+        <v>123.8</v>
       </c>
       <c r="N2">
-        <v>0.17307825445868</v>
+        <v>89.3303789372744</v>
       </c>
       <c r="O2">
-        <v>0.0771037844036697</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>2.42150008084074</v>
-      </c>
-      <c r="Q2" t="inlineStr">
+        <v>1.238</v>
+      </c>
+      <c r="Q2">
+        <v>0.119636406573179</v>
+      </c>
+      <c r="R2">
+        <v>0.150828486309082</v>
+      </c>
+      <c r="S2">
+        <v>0.06952925247954379</v>
+      </c>
+      <c r="T2">
+        <v>2.41973699515347</v>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>B2/B</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="S2">
-        <v>0.140001177506065</v>
-      </c>
-      <c r="T2">
-        <v>0.150366922879063</v>
-      </c>
-      <c r="U2">
-        <v>0.834876087904329</v>
-      </c>
-      <c r="V2">
-        <v>0.920390042963816</v>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
       </c>
       <c r="W2">
-        <v>-36.56114038259202</v>
+        <v>0.119636406573179</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>0.127910218542977</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>0.819849959918586</v>
       </c>
       <c r="Z2">
+        <v>0.903763690122217</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0.09270566997272503</v>
+      </c>
+      <c r="AC2">
+        <v>-6.390532544378699</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>1.69</v>
+      </c>
+      <c r="AF2">
+        <v>10.8</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
         <v>0.0388</v>
       </c>
-      <c r="AA2">
-        <v>123.7</v>
-      </c>
-      <c r="AB2">
-        <v>0.1212170033041622</v>
-      </c>
-      <c r="AC2">
-        <v>0.1028050458715596</v>
-      </c>
-      <c r="AD2">
+      <c r="AJ2">
+        <v>123.8</v>
+      </c>
+      <c r="AK2">
+        <v>0.09859902485231085</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="AM2">
         <v>0.25</v>
       </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-      <c r="AF2">
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>1.69</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
         <v>1</v>
       </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
-      <c r="AH2">
-        <v>10.8</v>
-      </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <v>0</v>
-      </c>
-      <c r="AL2">
-        <v>1.69</v>
-      </c>
-      <c r="AN2">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="b">
+      <c r="AX2">
         <v>1</v>
       </c>
-      <c r="AQ2">
-        <v>1</v>
+      <c r="AY2">
+        <v>10000000</v>
       </c>
     </row>
   </sheetData>
@@ -1304,7 +1363,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1337,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.0457</v>
+        <v>0.0447</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -1366,25 +1425,25 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1730782544586796</v>
+        <v>0.1508284863090817</v>
       </c>
       <c r="C3">
-        <v>91.99168924657113</v>
+        <v>88.09237893727442</v>
       </c>
       <c r="D3">
-        <v>93.22868924657112</v>
+        <v>89.33037893727442</v>
       </c>
       <c r="E3">
-        <v>1.237</v>
+        <v>1.238</v>
       </c>
       <c r="F3">
-        <v>1.237</v>
+        <v>1.238</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1399,37 +1458,37 @@
         <v>-10.8</v>
       </c>
       <c r="M3">
-        <v>0.2953956</v>
+        <v>0.2956344</v>
       </c>
       <c r="N3">
-        <v>-11.0953956</v>
+        <v>-11.0956344</v>
       </c>
       <c r="O3">
-        <v>-2.7738489</v>
+        <v>-2.7739086</v>
       </c>
       <c r="P3">
-        <v>-8.321546700000001</v>
+        <v>-8.321725800000001</v>
       </c>
       <c r="Q3">
-        <v>2.4784533</v>
+        <v>2.4782742</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1503669228790628</v>
+        <v>0.1279102185429767</v>
       </c>
       <c r="T3">
-        <v>0.9203900429638155</v>
+        <v>0.9037636901222174</v>
       </c>
       <c r="U3">
         <v>0.2388</v>
       </c>
       <c r="V3">
-        <v>-9.140285095648006</v>
+        <v>-9.132901989754913</v>
       </c>
       <c r="W3">
-        <v>2.421500080840744</v>
+        <v>2.419736995153473</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1437,7 +1496,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>-36.56114038259202</v>
+        <v>-36.53160795901966</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1448,25 +1507,25 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1750782544586796</v>
+        <v>0.1528284863090817</v>
       </c>
       <c r="C4">
-        <v>89.38647845436671</v>
+        <v>85.28757082065805</v>
       </c>
       <c r="D4">
-        <v>91.86047845436671</v>
+        <v>87.76357082065805</v>
       </c>
       <c r="E4">
-        <v>2.474</v>
+        <v>2.476</v>
       </c>
       <c r="F4">
-        <v>2.474</v>
+        <v>2.476</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1481,37 +1540,37 @@
         <v>-10.8</v>
       </c>
       <c r="M4">
-        <v>0.5907912000000001</v>
+        <v>0.5912688</v>
       </c>
       <c r="N4">
-        <v>-11.3907912</v>
+        <v>-11.3912688</v>
       </c>
       <c r="O4">
-        <v>-2.8476978</v>
+        <v>-2.8478172</v>
       </c>
       <c r="P4">
-        <v>-8.5430934</v>
+        <v>-8.543451600000001</v>
       </c>
       <c r="Q4">
-        <v>2.256906600000001</v>
+        <v>2.2565484</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1515053608676247</v>
+        <v>0.1288195064872928</v>
       </c>
       <c r="T4">
-        <v>0.9297817780960994</v>
+        <v>0.9129857685928524</v>
       </c>
       <c r="U4">
         <v>0.2388</v>
       </c>
       <c r="V4">
-        <v>-4.570142547824003</v>
+        <v>-4.566450994877457</v>
       </c>
       <c r="W4">
-        <v>1.330150040420372</v>
+        <v>1.329268497576737</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1519,7 +1578,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>-18.28057019129601</v>
+        <v>-18.26580397950983</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1530,25 +1589,25 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.1770782544586796</v>
+        <v>0.1548284863090817</v>
       </c>
       <c r="C5">
-        <v>86.8208461424537</v>
+        <v>82.53677730567813</v>
       </c>
       <c r="D5">
-        <v>90.5318461424537</v>
+        <v>86.25077730567813</v>
       </c>
       <c r="E5">
-        <v>3.711</v>
+        <v>3.714</v>
       </c>
       <c r="F5">
-        <v>3.711</v>
+        <v>3.714</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1563,37 +1622,37 @@
         <v>-10.8</v>
       </c>
       <c r="M5">
-        <v>0.8861868000000001</v>
+        <v>0.8869032</v>
       </c>
       <c r="N5">
-        <v>-11.6861868</v>
+        <v>-11.6869032</v>
       </c>
       <c r="O5">
-        <v>-2.9215467</v>
+        <v>-2.9217258</v>
       </c>
       <c r="P5">
-        <v>-8.764640100000001</v>
+        <v>-8.765177400000001</v>
       </c>
       <c r="Q5">
-        <v>2.0353599</v>
+        <v>2.0348226</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1526672718044043</v>
+        <v>0.1297475426366463</v>
       </c>
       <c r="T5">
-        <v>0.9393671572517293</v>
+        <v>0.9223979930113354</v>
       </c>
       <c r="U5">
         <v>0.2388</v>
       </c>
       <c r="V5">
-        <v>-3.046761698549335</v>
+        <v>-3.044300663251638</v>
       </c>
       <c r="W5">
-        <v>0.9663666936135814</v>
+        <v>0.9657789983844912</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1601,7 +1660,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>-12.18704679419734</v>
+        <v>-12.17720265300655</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1612,25 +1671,25 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1790782544586796</v>
+        <v>0.1568284863090816</v>
       </c>
       <c r="C6">
-        <v>84.29309945485329</v>
+        <v>79.83725255003883</v>
       </c>
       <c r="D6">
-        <v>89.24109945485328</v>
+        <v>84.78925255003882</v>
       </c>
       <c r="E6">
-        <v>4.948</v>
+        <v>4.952</v>
       </c>
       <c r="F6">
-        <v>4.948</v>
+        <v>4.952</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1645,37 +1704,37 @@
         <v>-10.8</v>
       </c>
       <c r="M6">
-        <v>1.1815824</v>
+        <v>1.1825376</v>
       </c>
       <c r="N6">
-        <v>-11.9815824</v>
+        <v>-11.9825376</v>
       </c>
       <c r="O6">
-        <v>-2.9953956</v>
+        <v>-2.9956344</v>
       </c>
       <c r="P6">
-        <v>-8.9861868</v>
+        <v>-8.9869032</v>
       </c>
       <c r="Q6">
-        <v>1.8138132</v>
+        <v>1.8130968</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1538533892190335</v>
+        <v>0.1306949128724447</v>
       </c>
       <c r="T6">
-        <v>0.9491522318064348</v>
+        <v>0.9320063054385367</v>
       </c>
       <c r="U6">
         <v>0.2388</v>
       </c>
       <c r="V6">
-        <v>-2.285071273912001</v>
+        <v>-2.283225497438728</v>
       </c>
       <c r="W6">
-        <v>0.784475020210186</v>
+        <v>0.7840342487883684</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1683,7 +1742,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>-9.140285095648006</v>
+        <v>-9.132901989754913</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1694,25 +1753,25 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1810782544586796</v>
+        <v>0.1588284863090816</v>
       </c>
       <c r="C7">
-        <v>81.80164072123465</v>
+        <v>77.18643372415278</v>
       </c>
       <c r="D7">
-        <v>87.98664072123465</v>
+        <v>83.37643372415278</v>
       </c>
       <c r="E7">
-        <v>6.185</v>
+        <v>6.19</v>
       </c>
       <c r="F7">
-        <v>6.185</v>
+        <v>6.19</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1727,37 +1786,37 @@
         <v>-10.8</v>
       </c>
       <c r="M7">
-        <v>1.476978</v>
+        <v>1.478172</v>
       </c>
       <c r="N7">
-        <v>-12.276978</v>
+        <v>-12.278172</v>
       </c>
       <c r="O7">
-        <v>-3.0692445</v>
+        <v>-3.069543</v>
       </c>
       <c r="P7">
-        <v>-9.207733500000002</v>
+        <v>-9.208629000000002</v>
       </c>
       <c r="Q7">
-        <v>1.592266499999999</v>
+        <v>1.591370999999999</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1550644775266023</v>
+        <v>0.1316622277447862</v>
       </c>
       <c r="T7">
-        <v>0.959143307930713</v>
+        <v>0.9418168981273635</v>
       </c>
       <c r="U7">
         <v>0.2388</v>
       </c>
       <c r="V7">
-        <v>-1.828057019129601</v>
+        <v>-1.826580397950982</v>
       </c>
       <c r="W7">
-        <v>0.6753400161681489</v>
+        <v>0.6749873990306946</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1765,7 +1824,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>-7.312228076518405</v>
+        <v>-7.306321591803931</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1776,25 +1835,25 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1830782544586796</v>
+        <v>0.1608284863090816</v>
       </c>
       <c r="C8">
-        <v>79.34496085954858</v>
+        <v>74.58192601360115</v>
       </c>
       <c r="D8">
-        <v>86.76696085954858</v>
+        <v>82.00992601360115</v>
       </c>
       <c r="E8">
-        <v>7.422</v>
+        <v>7.428</v>
       </c>
       <c r="F8">
-        <v>7.422</v>
+        <v>7.428</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1809,37 +1868,37 @@
         <v>-10.8</v>
       </c>
       <c r="M8">
-        <v>1.7723736</v>
+        <v>1.7738064</v>
       </c>
       <c r="N8">
-        <v>-12.5723736</v>
+        <v>-12.5738064</v>
       </c>
       <c r="O8">
-        <v>-3.1430934</v>
+        <v>-3.1434516</v>
       </c>
       <c r="P8">
-        <v>-9.429280200000001</v>
+        <v>-9.4303548</v>
       </c>
       <c r="Q8">
-        <v>1.3707198</v>
+        <v>1.369645200000001</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1563013336705023</v>
+        <v>0.1326501237846244</v>
       </c>
       <c r="T8">
-        <v>0.9693469601427419</v>
+        <v>0.9518362268308461</v>
       </c>
       <c r="U8">
         <v>0.2388</v>
       </c>
       <c r="V8">
-        <v>-1.523380849274668</v>
+        <v>-1.522150331625819</v>
       </c>
       <c r="W8">
-        <v>0.6025833468067907</v>
+        <v>0.6022894991922456</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1847,7 +1906,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>-6.093523397098671</v>
+        <v>-6.088601326503276</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1858,25 +1917,25 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1850782544586796</v>
+        <v>0.1628284863090816</v>
       </c>
       <c r="C9">
-        <v>76.92163331987919</v>
+        <v>72.02148907263532</v>
       </c>
       <c r="D9">
-        <v>85.5806333198792</v>
+        <v>80.68748907263532</v>
       </c>
       <c r="E9">
-        <v>8.659000000000001</v>
+        <v>8.666</v>
       </c>
       <c r="F9">
-        <v>8.659000000000001</v>
+        <v>8.666</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1891,37 +1950,37 @@
         <v>-10.8</v>
       </c>
       <c r="M9">
-        <v>2.0677692</v>
+        <v>2.0694408</v>
       </c>
       <c r="N9">
-        <v>-12.8677692</v>
+        <v>-12.8694408</v>
       </c>
       <c r="O9">
-        <v>-3.2169423</v>
+        <v>-3.2173602</v>
       </c>
       <c r="P9">
-        <v>-9.650826900000002</v>
+        <v>-9.652080600000001</v>
       </c>
       <c r="Q9">
-        <v>1.149173099999999</v>
+        <v>1.147919399999999</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1575647888712604</v>
+        <v>0.1336592649005881</v>
       </c>
       <c r="T9">
-        <v>0.9797700457356746</v>
+        <v>0.9620710249688121</v>
       </c>
       <c r="U9">
         <v>0.2388</v>
       </c>
       <c r="V9">
-        <v>-1.305755013664001</v>
+        <v>-1.304700284250702</v>
       </c>
       <c r="W9">
-        <v>0.5506142972629634</v>
+        <v>0.5503624278790675</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1929,7 +1988,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>-5.223020054656003</v>
+        <v>-5.218801137002808</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -1940,25 +1999,25 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1870782544586796</v>
+        <v>0.1648284863090816</v>
       </c>
       <c r="C10">
-        <v>74.53030851841305</v>
+        <v>69.50302476752971</v>
       </c>
       <c r="D10">
-        <v>84.42630851841305</v>
+        <v>79.40702476752971</v>
       </c>
       <c r="E10">
-        <v>9.896000000000001</v>
+        <v>9.904</v>
       </c>
       <c r="F10">
-        <v>9.896000000000001</v>
+        <v>9.904</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1973,37 +2032,37 @@
         <v>-10.8</v>
       </c>
       <c r="M10">
-        <v>2.3631648</v>
+        <v>2.3650752</v>
       </c>
       <c r="N10">
-        <v>-13.1631648</v>
+        <v>-13.1650752</v>
       </c>
       <c r="O10">
-        <v>-3.2907912</v>
+        <v>-3.2912688</v>
       </c>
       <c r="P10">
-        <v>-9.8723736</v>
+        <v>-9.873806399999999</v>
       </c>
       <c r="Q10">
-        <v>0.9276264000000012</v>
+        <v>0.9261936000000013</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1588557104894263</v>
+        <v>0.1346903438668988</v>
       </c>
       <c r="T10">
-        <v>0.990419720145845</v>
+        <v>0.9725283187184732</v>
       </c>
       <c r="U10">
         <v>0.2388</v>
       </c>
       <c r="V10">
-        <v>-1.142535636956001</v>
+        <v>-1.141612748719364</v>
       </c>
       <c r="W10">
-        <v>0.511637510105093</v>
+        <v>0.5114171243941842</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2011,7 +2070,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>-4.570142547824003</v>
+        <v>-4.566450994877457</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2022,25 +2081,25 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1890782544586796</v>
+        <v>0.1668284863090816</v>
       </c>
       <c r="C11">
-        <v>72.16970871586643</v>
+        <v>67.02456606873939</v>
       </c>
       <c r="D11">
-        <v>83.30270871586643</v>
+        <v>78.16656606873939</v>
       </c>
       <c r="E11">
-        <v>11.133</v>
+        <v>11.142</v>
       </c>
       <c r="F11">
-        <v>11.133</v>
+        <v>11.142</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -2055,37 +2114,37 @@
         <v>-10.8</v>
       </c>
       <c r="M11">
-        <v>2.6585604</v>
+        <v>2.6607096</v>
       </c>
       <c r="N11">
-        <v>-13.4585604</v>
+        <v>-13.4607096</v>
       </c>
       <c r="O11">
-        <v>-3.3646401</v>
+        <v>-3.3651774</v>
       </c>
       <c r="P11">
-        <v>-10.0939203</v>
+        <v>-10.0955322</v>
       </c>
       <c r="Q11">
-        <v>0.7060797000000001</v>
+        <v>0.7044677999999998</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1601750040112881</v>
+        <v>0.1357440839093922</v>
       </c>
       <c r="T11">
-        <v>1.001303453334261</v>
+        <v>0.9832154430999948</v>
       </c>
       <c r="U11">
         <v>0.2388</v>
       </c>
       <c r="V11">
-        <v>-1.015587232849779</v>
+        <v>-1.014766887750546</v>
       </c>
       <c r="W11">
-        <v>0.4813222312045272</v>
+        <v>0.4811263327948304</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2093,7 +2152,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>-4.062348931399113</v>
+        <v>-4.059067551002184</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2104,25 +2163,25 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1910782544586796</v>
+        <v>0.1688284863090816</v>
       </c>
       <c r="C12">
-        <v>69.83862329950816</v>
+        <v>64.58426696817251</v>
       </c>
       <c r="D12">
-        <v>82.20862329950816</v>
+        <v>76.96426696817251</v>
       </c>
       <c r="E12">
-        <v>12.37</v>
+        <v>12.38</v>
       </c>
       <c r="F12">
-        <v>12.37</v>
+        <v>12.38</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -2137,37 +2196,37 @@
         <v>-10.8</v>
       </c>
       <c r="M12">
-        <v>2.953956</v>
+        <v>2.956344000000001</v>
       </c>
       <c r="N12">
-        <v>-13.753956</v>
+        <v>-13.756344</v>
       </c>
       <c r="O12">
-        <v>-3.438489</v>
+        <v>-3.439086000000001</v>
       </c>
       <c r="P12">
-        <v>-10.315467</v>
+        <v>-10.317258</v>
       </c>
       <c r="Q12">
-        <v>0.4845330000000008</v>
+        <v>0.4827419999999982</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1615236151669691</v>
+        <v>0.1368212403972743</v>
       </c>
       <c r="T12">
-        <v>1.012429047260197</v>
+        <v>0.9941400591344391</v>
       </c>
       <c r="U12">
         <v>0.2388</v>
       </c>
       <c r="V12">
-        <v>-0.9140285095648005</v>
+        <v>-0.9132901989754912</v>
       </c>
       <c r="W12">
-        <v>0.4570700080840744</v>
+        <v>0.4568936995153473</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2175,7 +2234,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>-3.656114038259202</v>
+        <v>-3.653160795901965</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2186,25 +2245,25 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1930782544586796</v>
+        <v>0.1708284863090817</v>
       </c>
       <c r="C13">
-        <v>67.53590443215444</v>
+        <v>62.18039331287665</v>
       </c>
       <c r="D13">
-        <v>81.14290443215444</v>
+        <v>75.79839331287666</v>
       </c>
       <c r="E13">
-        <v>13.607</v>
+        <v>13.618</v>
       </c>
       <c r="F13">
-        <v>13.607</v>
+        <v>13.618</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -2219,37 +2278,37 @@
         <v>-10.8</v>
       </c>
       <c r="M13">
-        <v>3.2493516</v>
+        <v>3.2519784</v>
       </c>
       <c r="N13">
-        <v>-14.0493516</v>
+        <v>-14.0519784</v>
       </c>
       <c r="O13">
-        <v>-3.5123379</v>
+        <v>-3.5129946</v>
       </c>
       <c r="P13">
-        <v>-10.5370137</v>
+        <v>-10.5389838</v>
       </c>
       <c r="Q13">
-        <v>0.2629862999999997</v>
+        <v>0.2610162000000003</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.162902532191317</v>
+        <v>0.1379226026489291</v>
       </c>
       <c r="T13">
-        <v>1.023804654532783</v>
+        <v>1.005310172158422</v>
       </c>
       <c r="U13">
         <v>0.2388</v>
       </c>
       <c r="V13">
-        <v>-0.8309350086952733</v>
+        <v>-0.8302638172504467</v>
       </c>
       <c r="W13">
-        <v>0.4372272800764312</v>
+        <v>0.4370669995594068</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2257,7 +2316,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>-3.323740034781093</v>
+        <v>-3.321055269001787</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2268,25 +2327,25 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1950782544586796</v>
+        <v>0.1728284863090817</v>
       </c>
       <c r="C14">
-        <v>65.26046303525993</v>
+        <v>59.81131445941445</v>
       </c>
       <c r="D14">
-        <v>80.10446303525993</v>
+        <v>74.66731445941446</v>
       </c>
       <c r="E14">
-        <v>14.844</v>
+        <v>14.856</v>
       </c>
       <c r="F14">
-        <v>14.844</v>
+        <v>14.856</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -2301,37 +2360,37 @@
         <v>-10.8</v>
       </c>
       <c r="M14">
-        <v>3.5447472</v>
+        <v>3.5476128</v>
       </c>
       <c r="N14">
-        <v>-14.3447472</v>
+        <v>-14.3476128</v>
       </c>
       <c r="O14">
-        <v>-3.5861868</v>
+        <v>-3.5869032</v>
       </c>
       <c r="P14">
-        <v>-10.7585604</v>
+        <v>-10.7607096</v>
       </c>
       <c r="Q14">
-        <v>0.04143960000000035</v>
+        <v>0.0392904000000005</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1643127882389457</v>
+        <v>0.1390489958608488</v>
       </c>
       <c r="T14">
-        <v>1.035438798334293</v>
+        <v>1.016734151387495</v>
       </c>
       <c r="U14">
         <v>0.2388</v>
       </c>
       <c r="V14">
-        <v>-0.7616904246373338</v>
+        <v>-0.7610751658129095</v>
       </c>
       <c r="W14">
-        <v>0.4206916734033954</v>
+        <v>0.4205447495961228</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2339,7 +2398,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>-3.046761698549335</v>
+        <v>-3.044300663251638</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2350,25 +2409,25 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1970782544586796</v>
+        <v>0.1748284863090817</v>
       </c>
       <c r="C15">
-        <v>63.01126507655458</v>
+        <v>57.47549566446357</v>
       </c>
       <c r="D15">
-        <v>79.09226507655458</v>
+        <v>73.56949566446357</v>
       </c>
       <c r="E15">
-        <v>16.081</v>
+        <v>16.094</v>
       </c>
       <c r="F15">
-        <v>16.081</v>
+        <v>16.094</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -2383,37 +2442,37 @@
         <v>-10.8</v>
       </c>
       <c r="M15">
-        <v>3.8401428</v>
+        <v>3.8432472</v>
       </c>
       <c r="N15">
-        <v>-14.6401428</v>
+        <v>-14.6432472</v>
       </c>
       <c r="O15">
-        <v>-3.6600357</v>
+        <v>-3.6608118</v>
       </c>
       <c r="P15">
-        <v>-10.9801071</v>
+        <v>-10.9824354</v>
       </c>
       <c r="Q15">
-        <v>-0.1801071000000007</v>
+        <v>-0.1824353999999992</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1657554639658301</v>
+        <v>0.1402012831695942</v>
       </c>
       <c r="T15">
-        <v>1.047340393717445</v>
+        <v>1.02842075082873</v>
       </c>
       <c r="U15">
         <v>0.2388</v>
       </c>
       <c r="V15">
-        <v>-0.703098853511385</v>
+        <v>-0.7025309222888395</v>
       </c>
       <c r="W15">
-        <v>0.4067000062185188</v>
+        <v>0.4065643842425748</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2421,7 +2480,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>-2.81239541404554</v>
+        <v>-2.810123689155358</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2432,25 +2491,25 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1990782544586796</v>
+        <v>0.1768284863090817</v>
       </c>
       <c r="C16">
-        <v>60.78732813562421</v>
+        <v>55.17149113696737</v>
       </c>
       <c r="D16">
-        <v>78.10532813562421</v>
+        <v>72.50349113696737</v>
       </c>
       <c r="E16">
-        <v>17.318</v>
+        <v>17.332</v>
       </c>
       <c r="F16">
-        <v>17.318</v>
+        <v>17.332</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -2465,37 +2524,37 @@
         <v>-10.8</v>
       </c>
       <c r="M16">
-        <v>4.135538400000001</v>
+        <v>4.1388816</v>
       </c>
       <c r="N16">
-        <v>-14.9355384</v>
+        <v>-14.9388816</v>
       </c>
       <c r="O16">
-        <v>-3.733884600000001</v>
+        <v>-3.7347204</v>
       </c>
       <c r="P16">
-        <v>-11.2016538</v>
+        <v>-11.2041612</v>
       </c>
       <c r="Q16">
-        <v>-0.4016538000000018</v>
+        <v>-0.4041612000000008</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1672316902910142</v>
+        <v>0.1413803678576127</v>
       </c>
       <c r="T16">
-        <v>1.059518770388578</v>
+        <v>1.04037913165232</v>
       </c>
       <c r="U16">
         <v>0.2388</v>
       </c>
       <c r="V16">
-        <v>-0.6528775068320003</v>
+        <v>-0.6523501421253509</v>
       </c>
       <c r="W16">
-        <v>0.3947071486314817</v>
+        <v>0.3945812139395338</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2503,7 +2562,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>-2.611510027328002</v>
+        <v>-2.609400568501404</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2514,25 +2573,25 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.2010782544586796</v>
+        <v>0.1788284863090817</v>
       </c>
       <c r="C17">
-        <v>58.5877182234562</v>
+        <v>52.89793768569414</v>
       </c>
       <c r="D17">
-        <v>77.1427182234562</v>
+        <v>71.46793768569414</v>
       </c>
       <c r="E17">
-        <v>18.555</v>
+        <v>18.57</v>
       </c>
       <c r="F17">
-        <v>18.555</v>
+        <v>18.57</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -2547,37 +2606,37 @@
         <v>-10.8</v>
       </c>
       <c r="M17">
-        <v>4.430934000000001</v>
+        <v>4.434516</v>
       </c>
       <c r="N17">
-        <v>-15.230934</v>
+        <v>-15.234516</v>
       </c>
       <c r="O17">
-        <v>-3.8077335</v>
+        <v>-3.808629</v>
       </c>
       <c r="P17">
-        <v>-11.4232005</v>
+        <v>-11.425887</v>
       </c>
       <c r="Q17">
-        <v>-0.6232004999999994</v>
+        <v>-0.6258870000000005</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1687426513532614</v>
+        <v>0.1425871957147611</v>
       </c>
       <c r="T17">
-        <v>1.071983697099032</v>
+        <v>1.052618886142347</v>
       </c>
       <c r="U17">
         <v>0.2388</v>
       </c>
       <c r="V17">
-        <v>-0.609352339709867</v>
+        <v>-0.6088601326503276</v>
       </c>
       <c r="W17">
-        <v>0.3843133387227163</v>
+        <v>0.3841957996768983</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2585,7 +2644,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>-2.437409358839468</v>
+        <v>-2.43544053060131</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2596,25 +2655,25 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.2030782544586796</v>
+        <v>0.1808284863090817</v>
       </c>
       <c r="C18">
-        <v>56.41154683430729</v>
+        <v>50.6535489035147</v>
       </c>
       <c r="D18">
-        <v>76.20354683430729</v>
+        <v>70.4615489035147</v>
       </c>
       <c r="E18">
-        <v>19.792</v>
+        <v>19.808</v>
       </c>
       <c r="F18">
-        <v>19.792</v>
+        <v>19.808</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -2629,37 +2688,37 @@
         <v>-10.8</v>
       </c>
       <c r="M18">
-        <v>4.726329600000001</v>
+        <v>4.7301504</v>
       </c>
       <c r="N18">
-        <v>-15.5263296</v>
+        <v>-15.5301504</v>
       </c>
       <c r="O18">
-        <v>-3.8815824</v>
+        <v>-3.8825376</v>
       </c>
       <c r="P18">
-        <v>-11.6447472</v>
+        <v>-11.6476128</v>
       </c>
       <c r="Q18">
-        <v>-0.8447472000000005</v>
+        <v>-0.8476128000000003</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1702895876788955</v>
+        <v>0.1438227575685082</v>
       </c>
       <c r="T18">
-        <v>1.084745407778783</v>
+        <v>1.065150063358328</v>
       </c>
       <c r="U18">
         <v>0.2388</v>
       </c>
       <c r="V18">
-        <v>-0.5712678184780003</v>
+        <v>-0.5708063743596821</v>
       </c>
       <c r="W18">
-        <v>0.3752187550525465</v>
+        <v>0.3751085621970921</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2667,7 +2726,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>-2.285071273912001</v>
+        <v>-2.283225497438728</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2678,25 +2737,25 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.2050782544586796</v>
+        <v>0.1828284863090816</v>
       </c>
       <c r="C19">
-        <v>54.25796821033281</v>
+        <v>48.43710983622763</v>
       </c>
       <c r="D19">
-        <v>75.28696821033282</v>
+        <v>69.48310983622763</v>
       </c>
       <c r="E19">
-        <v>21.029</v>
+        <v>21.046</v>
       </c>
       <c r="F19">
-        <v>21.029</v>
+        <v>21.046</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -2711,37 +2770,37 @@
         <v>-10.8</v>
       </c>
       <c r="M19">
-        <v>5.021725200000001</v>
+        <v>5.0257848</v>
       </c>
       <c r="N19">
-        <v>-15.8217252</v>
+        <v>-15.8257848</v>
       </c>
       <c r="O19">
-        <v>-3.955431300000001</v>
+        <v>-3.9564462</v>
       </c>
       <c r="P19">
-        <v>-11.8662939</v>
+        <v>-11.8693386</v>
       </c>
       <c r="Q19">
-        <v>-1.066293900000002</v>
+        <v>-1.0693386</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1718737995786412</v>
+        <v>0.1450880919970445</v>
       </c>
       <c r="T19">
-        <v>1.09781462955925</v>
+        <v>1.077983196651802</v>
       </c>
       <c r="U19">
         <v>0.2388</v>
       </c>
       <c r="V19">
-        <v>-0.5376638291557649</v>
+        <v>-0.5372295288091126</v>
       </c>
       <c r="W19">
-        <v>0.3671941224023967</v>
+        <v>0.3670904114796161</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2749,7 +2808,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>-2.15065531662306</v>
+        <v>-2.14891811523645</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2760,25 +2819,25 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.2070782544586796</v>
+        <v>0.1848284863090817</v>
       </c>
       <c r="C20">
-        <v>52.12617680127624</v>
+        <v>46.24747208947783</v>
       </c>
       <c r="D20">
-        <v>74.39217680127624</v>
+        <v>68.53147208947783</v>
       </c>
       <c r="E20">
-        <v>22.266</v>
+        <v>22.284</v>
       </c>
       <c r="F20">
-        <v>22.266</v>
+        <v>22.284</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -2793,37 +2852,37 @@
         <v>-10.8</v>
       </c>
       <c r="M20">
-        <v>5.3171208</v>
+        <v>5.3214192</v>
       </c>
       <c r="N20">
-        <v>-16.1171208</v>
+        <v>-16.1214192</v>
       </c>
       <c r="O20">
-        <v>-4.029280200000001</v>
+        <v>-4.0303548</v>
       </c>
       <c r="P20">
-        <v>-12.0878406</v>
+        <v>-12.0910644</v>
       </c>
       <c r="Q20">
-        <v>-1.287840600000001</v>
+        <v>-1.2910644</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1734966507930149</v>
+        <v>0.1463842882409109</v>
       </c>
       <c r="T20">
-        <v>1.111202612846558</v>
+        <v>1.091129333196336</v>
       </c>
       <c r="U20">
         <v>0.2388</v>
       </c>
       <c r="V20">
-        <v>-0.5077936164248893</v>
+        <v>-0.507383443875273</v>
       </c>
       <c r="W20">
-        <v>0.3600611156022636</v>
+        <v>0.3599631663974152</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2831,7 +2890,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>-2.031174465699558</v>
+        <v>-2.029533775501092</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2842,25 +2901,25 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.2090782544586796</v>
+        <v>0.1868284863090817</v>
       </c>
       <c r="C21">
-        <v>50.01540490318189</v>
+        <v>44.08354933233519</v>
       </c>
       <c r="D21">
-        <v>73.51840490318189</v>
+        <v>67.60554933233519</v>
       </c>
       <c r="E21">
-        <v>23.503</v>
+        <v>23.522</v>
       </c>
       <c r="F21">
-        <v>23.503</v>
+        <v>23.522</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -2875,37 +2934,37 @@
         <v>-10.8</v>
       </c>
       <c r="M21">
-        <v>5.612516400000001</v>
+        <v>5.6170536</v>
       </c>
       <c r="N21">
-        <v>-16.4125164</v>
+        <v>-16.4170536</v>
       </c>
       <c r="O21">
-        <v>-4.1031291</v>
+        <v>-4.104263400000001</v>
       </c>
       <c r="P21">
-        <v>-12.3093873</v>
+        <v>-12.3127902</v>
       </c>
       <c r="Q21">
-        <v>-1.5093873</v>
+        <v>-1.512790200000001</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1751595724077434</v>
+        <v>0.1477124893303048</v>
       </c>
       <c r="T21">
-        <v>1.124921163622441</v>
+        <v>1.104600065704932</v>
       </c>
       <c r="U21">
         <v>0.2388</v>
       </c>
       <c r="V21">
-        <v>-0.4810676366130529</v>
+        <v>-0.4806790520923639</v>
       </c>
       <c r="W21">
-        <v>0.353678951623197</v>
+        <v>0.3535861576396565</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -2913,7 +2972,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>-1.924270546452212</v>
+        <v>-1.922716208369456</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -2924,25 +2983,25 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.2110782544586796</v>
+        <v>0.1888284863090817</v>
       </c>
       <c r="C22">
-        <v>47.92492046158261</v>
+        <v>41.94431316051836</v>
       </c>
       <c r="D22">
-        <v>72.66492046158261</v>
+        <v>66.70431316051837</v>
       </c>
       <c r="E22">
-        <v>24.74</v>
+        <v>24.76</v>
       </c>
       <c r="F22">
-        <v>24.74</v>
+        <v>24.76</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -2957,37 +3016,37 @@
         <v>-10.8</v>
       </c>
       <c r="M22">
-        <v>5.907912</v>
+        <v>5.912688000000001</v>
       </c>
       <c r="N22">
-        <v>-16.707912</v>
+        <v>-16.712688</v>
       </c>
       <c r="O22">
-        <v>-4.176978</v>
+        <v>-4.178172</v>
       </c>
       <c r="P22">
-        <v>-12.530934</v>
+        <v>-12.534516</v>
       </c>
       <c r="Q22">
-        <v>-1.730934</v>
+        <v>-1.734515999999999</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1768640670628402</v>
+        <v>0.1490738954469336</v>
       </c>
       <c r="T22">
-        <v>1.138982678167722</v>
+        <v>1.118407566526244</v>
       </c>
       <c r="U22">
         <v>0.2388</v>
       </c>
       <c r="V22">
-        <v>-0.4570142547824003</v>
+        <v>-0.4566450994877456</v>
       </c>
       <c r="W22">
-        <v>0.3479350040420372</v>
+        <v>0.3478468497576737</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -2995,7 +3054,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>-1.828057019129601</v>
+        <v>-1.826580397950982</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3006,25 +3065,25 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.2130782544586796</v>
+        <v>0.1908284863090816</v>
       </c>
       <c r="C23">
-        <v>45.8540250259497</v>
+        <v>39.82878928614519</v>
       </c>
       <c r="D23">
-        <v>71.8310250259497</v>
+        <v>65.82678928614519</v>
       </c>
       <c r="E23">
-        <v>25.977</v>
+        <v>25.998</v>
       </c>
       <c r="F23">
-        <v>25.977</v>
+        <v>25.998</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -3039,37 +3098,37 @@
         <v>-10.8</v>
       </c>
       <c r="M23">
-        <v>6.2033076</v>
+        <v>6.2083224</v>
       </c>
       <c r="N23">
-        <v>-17.0033076</v>
+        <v>-17.0083224</v>
       </c>
       <c r="O23">
-        <v>-4.2508269</v>
+        <v>-4.2520806</v>
       </c>
       <c r="P23">
-        <v>-12.7524807</v>
+        <v>-12.7562418</v>
       </c>
       <c r="Q23">
-        <v>-1.952480699999999</v>
+        <v>-1.956241800000001</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1786117134813572</v>
+        <v>0.1504697675411986</v>
       </c>
       <c r="T23">
-        <v>1.153400180423009</v>
+        <v>1.132564624330374</v>
       </c>
       <c r="U23">
         <v>0.2388</v>
       </c>
       <c r="V23">
-        <v>-0.4352516712213336</v>
+        <v>-0.434900094750234</v>
       </c>
       <c r="W23">
-        <v>0.3427380990876545</v>
+        <v>0.3426541426263559</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3077,7 +3136,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>-1.741006684885334</v>
+        <v>-1.739600379000936</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3088,25 +3147,25 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.2150782544586796</v>
+        <v>0.1928284863090817</v>
       </c>
       <c r="C24">
-        <v>43.80205184339204</v>
+        <v>37.73605402433061</v>
       </c>
       <c r="D24">
-        <v>71.01605184339203</v>
+        <v>64.97205402433062</v>
       </c>
       <c r="E24">
-        <v>27.214</v>
+        <v>27.236</v>
       </c>
       <c r="F24">
-        <v>27.214</v>
+        <v>27.236</v>
       </c>
       <c r="G24">
         <v>0</v>
       </c>
       <c r="H24">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -3121,37 +3180,37 @@
         <v>-10.8</v>
       </c>
       <c r="M24">
-        <v>6.4987032</v>
+        <v>6.5039568</v>
       </c>
       <c r="N24">
-        <v>-17.2987032</v>
+        <v>-17.3039568</v>
       </c>
       <c r="O24">
-        <v>-4.324675800000001</v>
+        <v>-4.3259892</v>
       </c>
       <c r="P24">
-        <v>-12.9740274</v>
+        <v>-12.9779676</v>
       </c>
       <c r="Q24">
-        <v>-2.1740274</v>
+        <v>-2.177967600000001</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1804041713465028</v>
+        <v>0.1519014312276243</v>
       </c>
       <c r="T24">
-        <v>1.168187362223304</v>
+        <v>1.147084683616661</v>
       </c>
       <c r="U24">
         <v>0.2388</v>
       </c>
       <c r="V24">
-        <v>-0.4154675043476366</v>
+        <v>-0.4151319086252234</v>
       </c>
       <c r="W24">
-        <v>0.3380136400382157</v>
+        <v>0.3379334997797034</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3159,7 +3218,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>-1.661870017390547</v>
+        <v>-1.660527634500894</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3170,25 +3229,25 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.2170782544586796</v>
+        <v>0.1948284863090817</v>
       </c>
       <c r="C25">
-        <v>41.76836408066939</v>
+        <v>35.66523104999727</v>
       </c>
       <c r="D25">
-        <v>70.21936408066939</v>
+        <v>64.13923104999728</v>
       </c>
       <c r="E25">
-        <v>28.451</v>
+        <v>28.474</v>
       </c>
       <c r="F25">
-        <v>28.451</v>
+        <v>28.474</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -3203,37 +3262,37 @@
         <v>-10.8</v>
       </c>
       <c r="M25">
-        <v>6.7940988</v>
+        <v>6.7995912</v>
       </c>
       <c r="N25">
-        <v>-17.5940988</v>
+        <v>-17.5995912</v>
       </c>
       <c r="O25">
-        <v>-4.3985247</v>
+        <v>-4.3998978</v>
       </c>
       <c r="P25">
-        <v>-13.1955741</v>
+        <v>-13.1996934</v>
       </c>
       <c r="Q25">
-        <v>-2.395574100000001</v>
+        <v>-2.399693399999999</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.182243186558795</v>
+        <v>0.1533702809838272</v>
       </c>
       <c r="T25">
-        <v>1.183358626667763</v>
+        <v>1.161981887299994</v>
       </c>
       <c r="U25">
         <v>0.2388</v>
       </c>
       <c r="V25">
-        <v>-0.3974036998107828</v>
+        <v>-0.3970826952067354</v>
       </c>
       <c r="W25">
-        <v>0.3337000035148149</v>
+        <v>0.3336233476153684</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3241,7 +3300,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>-1.589614799243131</v>
+        <v>-1.588330780826941</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3252,25 +3311,25 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.2190782544586796</v>
+        <v>0.1968284863090817</v>
       </c>
       <c r="C26">
-        <v>39.7523531645551</v>
+        <v>33.61548840095931</v>
       </c>
       <c r="D26">
-        <v>69.44035316455511</v>
+        <v>63.3274884009593</v>
       </c>
       <c r="E26">
-        <v>29.688</v>
+        <v>29.712</v>
       </c>
       <c r="F26">
-        <v>29.688</v>
+        <v>29.712</v>
       </c>
       <c r="G26">
         <v>0</v>
       </c>
       <c r="H26">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -3285,37 +3344,37 @@
         <v>-10.8</v>
       </c>
       <c r="M26">
-        <v>7.0894944</v>
+        <v>7.0952256</v>
       </c>
       <c r="N26">
-        <v>-17.8894944</v>
+        <v>-17.8952256</v>
       </c>
       <c r="O26">
-        <v>-4.4723736</v>
+        <v>-4.4738064</v>
       </c>
       <c r="P26">
-        <v>-13.4171208</v>
+        <v>-13.4214192</v>
       </c>
       <c r="Q26">
-        <v>-2.617120799999999</v>
+        <v>-2.621419199999998</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1841305969082529</v>
+        <v>0.1548777846809828</v>
       </c>
       <c r="T26">
-        <v>1.198929134913391</v>
+        <v>1.177271122659204</v>
       </c>
       <c r="U26">
         <v>0.2388</v>
       </c>
       <c r="V26">
-        <v>-0.3808452123186669</v>
+        <v>-0.3805375829064547</v>
       </c>
       <c r="W26">
-        <v>0.3297458367016977</v>
+        <v>0.3296723747980614</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3323,7 +3382,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>-1.523380849274667</v>
+        <v>-1.522150331625819</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3334,25 +3393,25 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.2210782544586796</v>
+        <v>0.1988284863090816</v>
       </c>
       <c r="C27">
-        <v>37.75343723145849</v>
+        <v>31.58603570573544</v>
       </c>
       <c r="D27">
-        <v>68.67843723145849</v>
+        <v>62.53603570573544</v>
       </c>
       <c r="E27">
-        <v>30.925</v>
+        <v>30.95</v>
       </c>
       <c r="F27">
-        <v>30.925</v>
+        <v>30.95</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -3367,37 +3426,37 @@
         <v>-10.8</v>
       </c>
       <c r="M27">
-        <v>7.38489</v>
+        <v>7.39086</v>
       </c>
       <c r="N27">
-        <v>-18.18489</v>
+        <v>-18.19086</v>
       </c>
       <c r="O27">
-        <v>-4.546222500000001</v>
+        <v>-4.547715</v>
       </c>
       <c r="P27">
-        <v>-13.6386675</v>
+        <v>-13.643145</v>
       </c>
       <c r="Q27">
-        <v>-2.838667500000001</v>
+        <v>-2.843145</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1860683382003629</v>
+        <v>0.1564254884767292</v>
       </c>
       <c r="T27">
-        <v>1.214914856712236</v>
+        <v>1.192968070961327</v>
       </c>
       <c r="U27">
         <v>0.2388</v>
       </c>
       <c r="V27">
-        <v>-0.3656114038259202</v>
+        <v>-0.3653160795901966</v>
       </c>
       <c r="W27">
-        <v>0.3261080032336298</v>
+        <v>0.326037479806139</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3405,7 +3464,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>-1.462445615303681</v>
+        <v>-1.461264318360786</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3416,25 +3475,25 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.2230782544586796</v>
+        <v>0.2008284863090816</v>
       </c>
       <c r="C28">
-        <v>35.77105967800593</v>
+        <v>29.57612161667281</v>
       </c>
       <c r="D28">
-        <v>67.93305967800593</v>
+        <v>61.76412161667281</v>
       </c>
       <c r="E28">
-        <v>32.162</v>
+        <v>32.188</v>
       </c>
       <c r="F28">
-        <v>32.162</v>
+        <v>32.188</v>
       </c>
       <c r="G28">
         <v>0</v>
       </c>
       <c r="H28">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -3449,37 +3508,37 @@
         <v>-10.8</v>
       </c>
       <c r="M28">
-        <v>7.6802856</v>
+        <v>7.686494400000001</v>
       </c>
       <c r="N28">
-        <v>-18.4802856</v>
+        <v>-18.4864944</v>
       </c>
       <c r="O28">
-        <v>-4.6200714</v>
+        <v>-4.6216236</v>
       </c>
       <c r="P28">
-        <v>-13.8602142</v>
+        <v>-13.8648708</v>
       </c>
       <c r="Q28">
-        <v>-3.060214200000001</v>
+        <v>-3.064870800000001</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1880584508787462</v>
+        <v>0.1580150221047931</v>
       </c>
       <c r="T28">
-        <v>1.231332625046186</v>
+        <v>1.209089261109453</v>
       </c>
       <c r="U28">
         <v>0.2388</v>
       </c>
       <c r="V28">
-        <v>-0.3515494267556925</v>
+        <v>-0.3512654611444198</v>
       </c>
       <c r="W28">
-        <v>0.3227500031092594</v>
+        <v>0.3226821921212875</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3487,7 +3546,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>-1.40619770702277</v>
+        <v>-1.405061844577679</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3498,25 +3557,25 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.2250782544586796</v>
+        <v>0.2028284863090817</v>
       </c>
       <c r="C29">
-        <v>33.80468780499351</v>
+        <v>27.58503143085851</v>
       </c>
       <c r="D29">
-        <v>67.20368780499351</v>
+        <v>61.01103143085851</v>
       </c>
       <c r="E29">
-        <v>33.399</v>
+        <v>33.426</v>
       </c>
       <c r="F29">
-        <v>33.399</v>
+        <v>33.426</v>
       </c>
       <c r="G29">
         <v>0</v>
       </c>
       <c r="H29">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -3531,37 +3590,37 @@
         <v>-10.8</v>
       </c>
       <c r="M29">
-        <v>7.9756812</v>
+        <v>7.982128800000001</v>
       </c>
       <c r="N29">
-        <v>-18.7756812</v>
+        <v>-18.7821288</v>
       </c>
       <c r="O29">
-        <v>-4.6939203</v>
+        <v>-4.695532200000001</v>
       </c>
       <c r="P29">
-        <v>-14.0817609</v>
+        <v>-14.0865966</v>
       </c>
       <c r="Q29">
-        <v>-3.2817609</v>
+        <v>-3.286596600000001</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1901030871921537</v>
+        <v>0.1596481045993793</v>
       </c>
       <c r="T29">
-        <v>1.248200195252298</v>
+        <v>1.225652127699993</v>
       </c>
       <c r="U29">
         <v>0.2388</v>
       </c>
       <c r="V29">
-        <v>-0.3385290776165928</v>
+        <v>-0.338255629250182</v>
       </c>
       <c r="W29">
-        <v>0.3196407437348424</v>
+        <v>0.3195754442649434</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3569,7 +3628,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>-1.354116310466371</v>
+        <v>-1.353022517000728</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3580,25 +3639,25 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.2270782544586796</v>
+        <v>0.2048284863090817</v>
       </c>
       <c r="C30">
-        <v>31.85381154776761</v>
+        <v>25.61208488298383</v>
       </c>
       <c r="D30">
-        <v>66.48981154776762</v>
+        <v>60.27608488298383</v>
       </c>
       <c r="E30">
-        <v>34.636</v>
+        <v>34.664</v>
       </c>
       <c r="F30">
-        <v>34.636</v>
+        <v>34.664</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
       <c r="H30">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -3613,37 +3672,37 @@
         <v>-10.8</v>
       </c>
       <c r="M30">
-        <v>8.271076800000001</v>
+        <v>8.277763200000001</v>
       </c>
       <c r="N30">
-        <v>-19.0710768</v>
+        <v>-19.0777632</v>
       </c>
       <c r="O30">
-        <v>-4.7677692</v>
+        <v>-4.7694408</v>
       </c>
       <c r="P30">
-        <v>-14.3033076</v>
+        <v>-14.3083224</v>
       </c>
       <c r="Q30">
-        <v>-3.503307599999999</v>
+        <v>-3.508322399999999</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1922045189587114</v>
+        <v>0.1613265504965929</v>
       </c>
       <c r="T30">
-        <v>1.265536309075246</v>
+        <v>1.242675073918049</v>
       </c>
       <c r="U30">
         <v>0.2388</v>
       </c>
       <c r="V30">
-        <v>-0.3264387534160001</v>
+        <v>-0.3261750710626755</v>
       </c>
       <c r="W30">
-        <v>0.3167535743157409</v>
+        <v>0.3166906069697669</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3651,7 +3710,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>-1.305755013664001</v>
+        <v>-1.304700284250702</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3662,25 +3721,25 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.2290782544586796</v>
+        <v>0.2068284863090816</v>
       </c>
       <c r="C31">
-        <v>29.91794228667496</v>
+        <v>23.65663409583448</v>
       </c>
       <c r="D31">
-        <v>65.79094228667496</v>
+        <v>59.55863409583447</v>
       </c>
       <c r="E31">
-        <v>35.873</v>
+        <v>35.90199999999999</v>
       </c>
       <c r="F31">
-        <v>35.873</v>
+        <v>35.90199999999999</v>
       </c>
       <c r="G31">
         <v>0</v>
       </c>
       <c r="H31">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -3695,37 +3754,37 @@
         <v>-10.8</v>
       </c>
       <c r="M31">
-        <v>8.5664724</v>
+        <v>8.5733976</v>
       </c>
       <c r="N31">
-        <v>-19.3664724</v>
+        <v>-19.3733976</v>
       </c>
       <c r="O31">
-        <v>-4.8416181</v>
+        <v>-4.8433494</v>
       </c>
       <c r="P31">
-        <v>-14.5248543</v>
+        <v>-14.5300482</v>
       </c>
       <c r="Q31">
-        <v>-3.724854299999999</v>
+        <v>-3.730048199999999</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1943651459862989</v>
+        <v>0.1630522765599252</v>
       </c>
       <c r="T31">
-        <v>1.283360764132644</v>
+        <v>1.260177539747881</v>
       </c>
       <c r="U31">
         <v>0.2388</v>
       </c>
       <c r="V31">
-        <v>-0.3151822446775174</v>
+        <v>-0.314927654819135</v>
       </c>
       <c r="W31">
-        <v>0.3140655200289912</v>
+        <v>0.3140047239708094</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3733,7 +3792,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>-1.26072897871007</v>
+        <v>-1.25971061927654</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3744,25 +3803,25 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.2310782544586796</v>
+        <v>0.2088284863090816</v>
       </c>
       <c r="C32">
-        <v>27.99661173175188</v>
+        <v>21.71806167542761</v>
       </c>
       <c r="D32">
-        <v>65.10661173175188</v>
+        <v>58.85806167542761</v>
       </c>
       <c r="E32">
-        <v>37.11</v>
+        <v>37.14</v>
       </c>
       <c r="F32">
-        <v>37.11</v>
+        <v>37.14</v>
       </c>
       <c r="G32">
         <v>0</v>
       </c>
       <c r="H32">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -3777,37 +3836,37 @@
         <v>-10.8</v>
       </c>
       <c r="M32">
-        <v>8.861868000000001</v>
+        <v>8.869032000000001</v>
       </c>
       <c r="N32">
-        <v>-19.661868</v>
+        <v>-19.669032</v>
       </c>
       <c r="O32">
-        <v>-4.915467</v>
+        <v>-4.917258</v>
       </c>
       <c r="P32">
-        <v>-14.746401</v>
+        <v>-14.751774</v>
       </c>
       <c r="Q32">
-        <v>-3.946401000000002</v>
+        <v>-3.951774</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1965875052146746</v>
+        <v>0.1648273090822099</v>
       </c>
       <c r="T32">
-        <v>1.301694489334539</v>
+        <v>1.278180076029993</v>
       </c>
       <c r="U32">
         <v>0.2388</v>
       </c>
       <c r="V32">
-        <v>-0.3046761698549335</v>
+        <v>-0.3044300663251638</v>
       </c>
       <c r="W32">
-        <v>0.3115566693613581</v>
+        <v>0.3114978998384491</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3815,7 +3874,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>-1.218704679419734</v>
+        <v>-1.217720265300655</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3826,25 +3885,25 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.2330782544586796</v>
+        <v>0.2108284863090816</v>
       </c>
       <c r="C33">
-        <v>26.08937087630299</v>
+        <v>19.79577893902454</v>
       </c>
       <c r="D33">
-        <v>64.43637087630299</v>
+        <v>58.17377893902454</v>
       </c>
       <c r="E33">
-        <v>38.347</v>
+        <v>38.378</v>
       </c>
       <c r="F33">
-        <v>38.347</v>
+        <v>38.378</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -3859,37 +3918,37 @@
         <v>-10.8</v>
       </c>
       <c r="M33">
-        <v>9.1572636</v>
+        <v>9.1646664</v>
       </c>
       <c r="N33">
-        <v>-19.9572636</v>
+        <v>-19.9646664</v>
       </c>
       <c r="O33">
-        <v>-4.9893159</v>
+        <v>-4.9911666</v>
       </c>
       <c r="P33">
-        <v>-14.9679477</v>
+        <v>-14.9734998</v>
       </c>
       <c r="Q33">
-        <v>-4.167947699999999</v>
+        <v>-4.173499799999998</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1988742806525684</v>
+        <v>0.1666537918225318</v>
       </c>
       <c r="T33">
-        <v>1.320559626861127</v>
+        <v>1.296704424957964</v>
       </c>
       <c r="U33">
         <v>0.2388</v>
       </c>
       <c r="V33">
-        <v>-0.294847906311226</v>
+        <v>-0.2946097416049973</v>
       </c>
       <c r="W33">
-        <v>0.3092096800271208</v>
+        <v>0.3091528062952734</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -3897,7 +3956,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>-1.179391625244904</v>
+        <v>-1.178438966419989</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -3908,25 +3967,25 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.2350782544586796</v>
+        <v>0.2128284863090817</v>
       </c>
       <c r="C34">
-        <v>24.19578901445576</v>
+        <v>17.88922426532927</v>
       </c>
       <c r="D34">
-        <v>63.77978901445576</v>
+        <v>57.50522426532927</v>
       </c>
       <c r="E34">
-        <v>39.584</v>
+        <v>39.616</v>
       </c>
       <c r="F34">
-        <v>39.584</v>
+        <v>39.616</v>
       </c>
       <c r="G34">
         <v>0</v>
       </c>
       <c r="H34">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -3941,37 +4000,37 @@
         <v>-10.8</v>
       </c>
       <c r="M34">
-        <v>9.452659200000001</v>
+        <v>9.460300800000001</v>
       </c>
       <c r="N34">
-        <v>-20.2526592</v>
+        <v>-20.2603008</v>
       </c>
       <c r="O34">
-        <v>-5.063164800000001</v>
+        <v>-5.065075200000001</v>
       </c>
       <c r="P34">
-        <v>-15.1894944</v>
+        <v>-15.1952256</v>
       </c>
       <c r="Q34">
-        <v>-4.389494400000002</v>
+        <v>-4.395225600000002</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.2012283141915767</v>
+        <v>0.1685339946434514</v>
       </c>
       <c r="T34">
-        <v>1.33997962137379</v>
+        <v>1.315773607677934</v>
       </c>
       <c r="U34">
         <v>0.2388</v>
       </c>
       <c r="V34">
-        <v>-0.2856339092390002</v>
+        <v>-0.285403187179841</v>
       </c>
       <c r="W34">
-        <v>0.3070093775262732</v>
+        <v>0.3069542810985461</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -3979,7 +4038,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>-1.142535636956001</v>
+        <v>-1.141612748719365</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -3990,25 +4049,25 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.2370782544586796</v>
+        <v>0.2148284863090816</v>
       </c>
       <c r="C35">
-        <v>22.31545281817359</v>
+        <v>15.99786155715535</v>
       </c>
       <c r="D35">
-        <v>63.13645281817359</v>
+        <v>56.85186155715535</v>
       </c>
       <c r="E35">
-        <v>40.82100000000001</v>
+        <v>40.854</v>
       </c>
       <c r="F35">
-        <v>40.82100000000001</v>
+        <v>40.854</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
       <c r="H35">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -4023,37 +4082,37 @@
         <v>-10.8</v>
       </c>
       <c r="M35">
-        <v>9.748054800000002</v>
+        <v>9.7559352</v>
       </c>
       <c r="N35">
-        <v>-20.5480548</v>
+        <v>-20.5559352</v>
       </c>
       <c r="O35">
-        <v>-5.137013700000001</v>
+        <v>-5.1389838</v>
       </c>
       <c r="P35">
-        <v>-15.4110411</v>
+        <v>-15.4169514</v>
       </c>
       <c r="Q35">
-        <v>-4.611041100000001</v>
+        <v>-4.6169514</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.2036526173884659</v>
+        <v>0.1704703229217118</v>
       </c>
       <c r="T35">
-        <v>1.35997931721519</v>
+        <v>1.335412019732829</v>
       </c>
       <c r="U35">
         <v>0.2388</v>
       </c>
       <c r="V35">
-        <v>-0.2769783362317577</v>
+        <v>-0.2767546057501489</v>
       </c>
       <c r="W35">
-        <v>0.3049424266921438</v>
+        <v>0.3048889998531356</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4061,7 +4120,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>-1.107913344927031</v>
+        <v>-1.107018423000595</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4072,25 +4131,25 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.2390782544586796</v>
+        <v>0.2168284863090816</v>
       </c>
       <c r="C36">
-        <v>20.4479654695713</v>
+        <v>14.12117880771656</v>
       </c>
       <c r="D36">
-        <v>62.50596546957131</v>
+        <v>56.21317880771656</v>
       </c>
       <c r="E36">
-        <v>42.05800000000001</v>
+        <v>42.092</v>
       </c>
       <c r="F36">
-        <v>42.05800000000001</v>
+        <v>42.092</v>
       </c>
       <c r="G36">
         <v>0</v>
       </c>
       <c r="H36">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -4105,37 +4164,37 @@
         <v>-10.8</v>
       </c>
       <c r="M36">
-        <v>10.0434504</v>
+        <v>10.0515696</v>
       </c>
       <c r="N36">
-        <v>-20.8434504</v>
+        <v>-20.8515696</v>
       </c>
       <c r="O36">
-        <v>-5.2108626</v>
+        <v>-5.2128924</v>
       </c>
       <c r="P36">
-        <v>-15.6325878</v>
+        <v>-15.6386772</v>
       </c>
       <c r="Q36">
-        <v>-4.832587800000001</v>
+        <v>-4.838677199999999</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.2061503843185942</v>
+        <v>0.1724653278144651</v>
       </c>
       <c r="T36">
-        <v>1.380585064445723</v>
+        <v>1.355645535183326</v>
       </c>
       <c r="U36">
         <v>0.2388</v>
       </c>
       <c r="V36">
-        <v>-0.2688319145778825</v>
+        <v>-0.2686147644045563</v>
       </c>
       <c r="W36">
-        <v>0.3029970612011983</v>
+        <v>0.302945205739808</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4143,7 +4202,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>-1.075327658311529</v>
+        <v>-1.074459057618225</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4154,25 +4213,25 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.2410782544586796</v>
+        <v>0.2188284863090816</v>
       </c>
       <c r="C37">
-        <v>18.59294584470511</v>
+        <v>12.25868676248314</v>
       </c>
       <c r="D37">
-        <v>61.88794584470511</v>
+        <v>55.58868676248314</v>
       </c>
       <c r="E37">
-        <v>43.295</v>
+        <v>43.33000000000001</v>
       </c>
       <c r="F37">
-        <v>43.295</v>
+        <v>43.33000000000001</v>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
       <c r="H37">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -4187,37 +4246,37 @@
         <v>-10.8</v>
       </c>
       <c r="M37">
-        <v>10.338846</v>
+        <v>10.347204</v>
       </c>
       <c r="N37">
-        <v>-21.138846</v>
+        <v>-21.147204</v>
       </c>
       <c r="O37">
-        <v>-5.2847115</v>
+        <v>-5.286801000000001</v>
       </c>
       <c r="P37">
-        <v>-15.8541345</v>
+        <v>-15.860403</v>
       </c>
       <c r="Q37">
-        <v>-5.0541345</v>
+        <v>-5.060403000000001</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.2087250056158033</v>
+        <v>0.1745217174731491</v>
       </c>
       <c r="T37">
-        <v>1.401824834667965</v>
+        <v>1.376501620339993</v>
       </c>
       <c r="U37">
         <v>0.2388</v>
       </c>
       <c r="V37">
-        <v>-0.2611510027328002</v>
+        <v>-0.2609400568501404</v>
       </c>
       <c r="W37">
-        <v>0.3011628594525927</v>
+        <v>0.3011124855758135</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4225,7 +4284,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>-1.0446040109312</v>
+        <v>-1.043760227400561</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4236,25 +4295,25 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.2430782544586796</v>
+        <v>0.2208284863090816</v>
       </c>
       <c r="C38">
-        <v>16.75002774530972</v>
+        <v>10.40991766925347</v>
       </c>
       <c r="D38">
-        <v>61.28202774530971</v>
+        <v>54.97791766925347</v>
       </c>
       <c r="E38">
-        <v>44.532</v>
+        <v>44.568</v>
       </c>
       <c r="F38">
-        <v>44.532</v>
+        <v>44.568</v>
       </c>
       <c r="G38">
         <v>0</v>
       </c>
       <c r="H38">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -4269,37 +4328,37 @@
         <v>-10.8</v>
       </c>
       <c r="M38">
-        <v>10.6342416</v>
+        <v>10.6428384</v>
       </c>
       <c r="N38">
-        <v>-21.4342416</v>
+        <v>-21.4428384</v>
       </c>
       <c r="O38">
-        <v>-5.3585604</v>
+        <v>-5.3607096</v>
       </c>
       <c r="P38">
-        <v>-16.0756812</v>
+        <v>-16.0821288</v>
       </c>
       <c r="Q38">
-        <v>-5.275681199999998</v>
+        <v>-5.282128799999999</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.2113800838285503</v>
+        <v>0.1766423693086671</v>
       </c>
       <c r="T38">
-        <v>1.423728347709652</v>
+        <v>1.398009458157805</v>
       </c>
       <c r="U38">
         <v>0.2388</v>
       </c>
       <c r="V38">
-        <v>-0.2538968082124446</v>
+        <v>-0.2536917219376365</v>
       </c>
       <c r="W38">
-        <v>0.2994305578011318</v>
+        <v>0.2993815831987076</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4307,7 +4366,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>-1.015587232849779</v>
+        <v>-1.014766887750546</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4318,25 +4377,25 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.2450782544586796</v>
+        <v>0.2228284863090817</v>
       </c>
       <c r="C39">
-        <v>14.91885917522822</v>
+        <v>8.574424109730131</v>
       </c>
       <c r="D39">
-        <v>60.68785917522822</v>
+        <v>54.38042410973013</v>
       </c>
       <c r="E39">
-        <v>45.769</v>
+        <v>45.806</v>
       </c>
       <c r="F39">
-        <v>45.769</v>
+        <v>45.806</v>
       </c>
       <c r="G39">
         <v>0</v>
       </c>
       <c r="H39">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -4351,37 +4410,37 @@
         <v>-10.8</v>
       </c>
       <c r="M39">
-        <v>10.9296372</v>
+        <v>10.9384728</v>
       </c>
       <c r="N39">
-        <v>-21.7296372</v>
+        <v>-21.7384728</v>
       </c>
       <c r="O39">
-        <v>-5.4324093</v>
+        <v>-5.4346182</v>
       </c>
       <c r="P39">
-        <v>-16.2972279</v>
+        <v>-16.3038546</v>
       </c>
       <c r="Q39">
-        <v>-5.497227899999999</v>
+        <v>-5.5038546</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.2141194502385273</v>
+        <v>0.1788303434246777</v>
       </c>
       <c r="T39">
-        <v>1.44632721037171</v>
+        <v>1.42020008447777</v>
       </c>
       <c r="U39">
         <v>0.2388</v>
       </c>
       <c r="V39">
-        <v>-0.247034732314811</v>
+        <v>-0.246835188912295</v>
       </c>
       <c r="W39">
-        <v>0.2977918940767769</v>
+        <v>0.2977442431122561</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4389,7 +4448,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>-0.9881389292592437</v>
+        <v>-0.98734075564918</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4400,25 +4459,25 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.2470782544586796</v>
+        <v>0.2248284863090816</v>
       </c>
       <c r="C40">
-        <v>13.0991016585306</v>
+        <v>6.751777906466629</v>
       </c>
       <c r="D40">
-        <v>60.1051016585306</v>
+        <v>53.79577790646663</v>
       </c>
       <c r="E40">
-        <v>47.006</v>
+        <v>47.044</v>
       </c>
       <c r="F40">
-        <v>47.006</v>
+        <v>47.044</v>
       </c>
       <c r="G40">
         <v>0</v>
       </c>
       <c r="H40">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -4433,37 +4492,37 @@
         <v>-10.8</v>
       </c>
       <c r="M40">
-        <v>11.2250328</v>
+        <v>11.2341072</v>
       </c>
       <c r="N40">
-        <v>-22.0250328</v>
+        <v>-22.0341072</v>
       </c>
       <c r="O40">
-        <v>-5.5062582</v>
+        <v>-5.5085268</v>
       </c>
       <c r="P40">
-        <v>-16.5187746</v>
+        <v>-16.5255804</v>
       </c>
       <c r="Q40">
-        <v>-5.7187746</v>
+        <v>-5.725580400000002</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.2169471833068906</v>
+        <v>0.1810888973508821</v>
       </c>
       <c r="T40">
-        <v>1.469655068603512</v>
+        <v>1.443106537453218</v>
       </c>
       <c r="U40">
         <v>0.2388</v>
       </c>
       <c r="V40">
-        <v>-0.2405338183065265</v>
+        <v>-0.2403395260461819</v>
       </c>
       <c r="W40">
-        <v>0.2962394758115985</v>
+        <v>0.2961930788198283</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4471,7 +4530,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>-0.9621352732261059</v>
+        <v>-0.9613581041847277</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4482,25 +4541,25 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.2490782544586796</v>
+        <v>0.2268284863090817</v>
       </c>
       <c r="C41">
-        <v>11.29042959654532</v>
+        <v>4.941569099573002</v>
       </c>
       <c r="D41">
-        <v>59.53342959654532</v>
+        <v>53.22356909957301</v>
       </c>
       <c r="E41">
-        <v>48.243</v>
+        <v>48.282</v>
       </c>
       <c r="F41">
-        <v>48.243</v>
+        <v>48.282</v>
       </c>
       <c r="G41">
         <v>0</v>
       </c>
       <c r="H41">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -4515,37 +4574,37 @@
         <v>-10.8</v>
       </c>
       <c r="M41">
-        <v>11.5204284</v>
+        <v>11.5297416</v>
       </c>
       <c r="N41">
-        <v>-22.3204284</v>
+        <v>-22.3297416</v>
       </c>
       <c r="O41">
-        <v>-5.580107100000001</v>
+        <v>-5.5824354</v>
       </c>
       <c r="P41">
-        <v>-16.74032130000001</v>
+        <v>-16.7473062</v>
       </c>
       <c r="Q41">
-        <v>-5.940321300000004</v>
+        <v>-5.9473062</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.2198676289348724</v>
+        <v>0.1834215022254868</v>
       </c>
       <c r="T41">
-        <v>1.493747774646192</v>
+        <v>1.466764021673763</v>
       </c>
       <c r="U41">
         <v>0.2388</v>
       </c>
       <c r="V41">
-        <v>-0.234366284503795</v>
+        <v>-0.2341769740962798</v>
       </c>
       <c r="W41">
-        <v>0.2947666687395062</v>
+        <v>0.2947214614141916</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4553,7 +4612,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>-0.9374651380151802</v>
+        <v>-0.9367078963851192</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4564,25 +4623,25 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.2510782544586796</v>
+        <v>0.2288284863090816</v>
       </c>
       <c r="C42">
-        <v>9.492529661237675</v>
+        <v>3.14340498804075</v>
       </c>
       <c r="D42">
-        <v>58.97252966123768</v>
+        <v>52.66340498804075</v>
       </c>
       <c r="E42">
-        <v>49.48</v>
+        <v>49.52</v>
       </c>
       <c r="F42">
-        <v>49.48</v>
+        <v>49.52</v>
       </c>
       <c r="G42">
         <v>0</v>
       </c>
       <c r="H42">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -4597,37 +4656,37 @@
         <v>-10.8</v>
       </c>
       <c r="M42">
-        <v>11.815824</v>
+        <v>11.825376</v>
       </c>
       <c r="N42">
-        <v>-22.615824</v>
+        <v>-22.625376</v>
       </c>
       <c r="O42">
-        <v>-5.653956000000001</v>
+        <v>-5.656344000000001</v>
       </c>
       <c r="P42">
-        <v>-16.961868</v>
+        <v>-16.969032</v>
       </c>
       <c r="Q42">
-        <v>-6.161868000000002</v>
+        <v>-6.169032000000001</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.2228854227504536</v>
+        <v>0.1858318605959115</v>
       </c>
       <c r="T42">
-        <v>1.518643570890296</v>
+        <v>1.491210088701659</v>
       </c>
       <c r="U42">
         <v>0.2388</v>
       </c>
       <c r="V42">
-        <v>-0.2285071273912001</v>
+        <v>-0.2283225497438728</v>
       </c>
       <c r="W42">
-        <v>0.2933675020210186</v>
+        <v>0.2933234248788368</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4635,7 +4694,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>-0.9140285095648006</v>
+        <v>-0.9132901989754914</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4646,25 +4705,25 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.2530782544586796</v>
+        <v>0.2308284863090816</v>
       </c>
       <c r="C43">
-        <v>7.705100222560226</v>
+        <v>1.356909230976086</v>
       </c>
       <c r="D43">
-        <v>58.42210022256023</v>
+        <v>52.11490923097609</v>
       </c>
       <c r="E43">
-        <v>50.71700000000001</v>
+        <v>50.758</v>
       </c>
       <c r="F43">
-        <v>50.71700000000001</v>
+        <v>50.758</v>
       </c>
       <c r="G43">
         <v>0</v>
       </c>
       <c r="H43">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -4679,37 +4738,37 @@
         <v>-10.8</v>
       </c>
       <c r="M43">
-        <v>12.1112196</v>
+        <v>12.1210104</v>
       </c>
       <c r="N43">
-        <v>-22.9112196</v>
+        <v>-22.9210104</v>
       </c>
       <c r="O43">
-        <v>-5.727804900000001</v>
+        <v>-5.7302526</v>
       </c>
       <c r="P43">
-        <v>-17.1834147</v>
+        <v>-17.1907578</v>
       </c>
       <c r="Q43">
-        <v>-6.383414699999999</v>
+        <v>-6.390757799999999</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.2260055146614783</v>
+        <v>0.1883239260297405</v>
       </c>
       <c r="T43">
-        <v>1.544383292430809</v>
+        <v>1.516484835967788</v>
       </c>
       <c r="U43">
         <v>0.2388</v>
       </c>
       <c r="V43">
-        <v>-0.222933782820683</v>
+        <v>-0.222753707067193</v>
       </c>
       <c r="W43">
-        <v>0.2920365873375791</v>
+        <v>0.2919935852476457</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4717,7 +4776,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>-0.8917351312827322</v>
+        <v>-0.8910148282687718</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4728,25 +4787,25 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.2550782544586797</v>
+        <v>0.2328284863090817</v>
       </c>
       <c r="C44">
-        <v>5.92785080757595</v>
+        <v>-0.4182789955811046</v>
       </c>
       <c r="D44">
-        <v>57.88185080757595</v>
+        <v>51.57772100441889</v>
       </c>
       <c r="E44">
-        <v>51.954</v>
+        <v>51.996</v>
       </c>
       <c r="F44">
-        <v>51.954</v>
+        <v>51.996</v>
       </c>
       <c r="G44">
         <v>0</v>
       </c>
       <c r="H44">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -4761,37 +4820,37 @@
         <v>-10.8</v>
       </c>
       <c r="M44">
-        <v>12.4066152</v>
+        <v>12.4166448</v>
       </c>
       <c r="N44">
-        <v>-23.2066152</v>
+        <v>-23.2166448</v>
       </c>
       <c r="O44">
-        <v>-5.8016538</v>
+        <v>-5.8041612</v>
       </c>
       <c r="P44">
-        <v>-17.4049614</v>
+        <v>-17.4124836</v>
       </c>
       <c r="Q44">
-        <v>-6.604961400000001</v>
+        <v>-6.612483600000001</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.2292331959487451</v>
+        <v>0.1909019247543912</v>
       </c>
       <c r="T44">
-        <v>1.571010590576168</v>
+        <v>1.542631126243095</v>
       </c>
       <c r="U44">
         <v>0.2388</v>
       </c>
       <c r="V44">
-        <v>-0.2176258356106668</v>
+        <v>-0.217450047375117</v>
       </c>
       <c r="W44">
-        <v>0.2907690495438273</v>
+        <v>0.290727071313178</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4799,7 +4858,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>-0.8705033424426671</v>
+        <v>-0.8698001895004679</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4810,25 +4869,25 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.2570782544586797</v>
+        <v>0.2348284863090817</v>
       </c>
       <c r="C45">
-        <v>4.160501589316709</v>
+        <v>-2.182505790222521</v>
       </c>
       <c r="D45">
-        <v>57.35150158931671</v>
+        <v>51.05149420977747</v>
       </c>
       <c r="E45">
-        <v>53.191</v>
+        <v>53.23399999999999</v>
       </c>
       <c r="F45">
-        <v>53.191</v>
+        <v>53.23399999999999</v>
       </c>
       <c r="G45">
         <v>0</v>
       </c>
       <c r="H45">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -4843,37 +4902,37 @@
         <v>-10.8</v>
       </c>
       <c r="M45">
-        <v>12.7020108</v>
+        <v>12.7122792</v>
       </c>
       <c r="N45">
-        <v>-23.5020108</v>
+        <v>-23.5122792</v>
       </c>
       <c r="O45">
-        <v>-5.8755027</v>
+        <v>-5.8780698</v>
       </c>
       <c r="P45">
-        <v>-17.6265081</v>
+        <v>-17.6342094</v>
       </c>
       <c r="Q45">
-        <v>-6.826508100000002</v>
+        <v>-6.834209400000002</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.2325741292110038</v>
+        <v>0.1935703795746437</v>
       </c>
       <c r="T45">
-        <v>1.598572179884522</v>
+        <v>1.569694830212272</v>
       </c>
       <c r="U45">
         <v>0.2388</v>
       </c>
       <c r="V45">
-        <v>-0.2125647696662327</v>
+        <v>-0.212393069529184</v>
       </c>
       <c r="W45">
-        <v>0.2895604669962964</v>
+        <v>0.2895194650035692</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -4881,7 +4940,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>-0.8502590786649304</v>
+        <v>-0.8495722781167363</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -4892,25 +4951,25 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.2590782544586796</v>
+        <v>0.2368284863090817</v>
       </c>
       <c r="C46">
-        <v>2.402782903486795</v>
+        <v>-3.936103269769959</v>
       </c>
       <c r="D46">
-        <v>56.8307829034868</v>
+        <v>50.53589673023004</v>
       </c>
       <c r="E46">
-        <v>54.428</v>
+        <v>54.472</v>
       </c>
       <c r="F46">
-        <v>54.428</v>
+        <v>54.472</v>
       </c>
       <c r="G46">
         <v>0</v>
       </c>
       <c r="H46">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -4925,37 +4984,37 @@
         <v>-10.8</v>
       </c>
       <c r="M46">
-        <v>12.9974064</v>
+        <v>13.0079136</v>
       </c>
       <c r="N46">
-        <v>-23.7974064</v>
+        <v>-23.8079136</v>
       </c>
       <c r="O46">
-        <v>-5.9493516</v>
+        <v>-5.9519784</v>
       </c>
       <c r="P46">
-        <v>-17.8480548</v>
+        <v>-17.8559352</v>
       </c>
       <c r="Q46">
-        <v>-7.048054799999999</v>
+        <v>-7.055935199999997</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.2360343815183432</v>
+        <v>0.1963341363527624</v>
       </c>
       <c r="T46">
-        <v>1.627118111668174</v>
+        <v>1.597725095037492</v>
       </c>
       <c r="U46">
         <v>0.2388</v>
       </c>
       <c r="V46">
-        <v>-0.2077337521738183</v>
+        <v>-0.2075659543126117</v>
       </c>
       <c r="W46">
-        <v>0.2884068200191078</v>
+        <v>0.2883667498898517</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -4963,7 +5022,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>-0.8309350086952731</v>
+        <v>-0.8302638172504466</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -4974,25 +5033,25 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.2610782544586797</v>
+        <v>0.2388284863090817</v>
       </c>
       <c r="C47">
-        <v>0.6544347912579269</v>
+        <v>-5.679390268264193</v>
       </c>
       <c r="D47">
-        <v>56.31943479125793</v>
+        <v>50.03060973173581</v>
       </c>
       <c r="E47">
-        <v>55.665</v>
+        <v>55.71</v>
       </c>
       <c r="F47">
-        <v>55.665</v>
+        <v>55.71</v>
       </c>
       <c r="G47">
         <v>0</v>
       </c>
       <c r="H47">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -5007,37 +5066,37 @@
         <v>-10.8</v>
       </c>
       <c r="M47">
-        <v>13.292802</v>
+        <v>13.303548</v>
       </c>
       <c r="N47">
-        <v>-24.092802</v>
+        <v>-24.103548</v>
       </c>
       <c r="O47">
-        <v>-6.0232005</v>
+        <v>-6.025887000000001</v>
       </c>
       <c r="P47">
-        <v>-18.0696015</v>
+        <v>-18.077661</v>
       </c>
       <c r="Q47">
-        <v>-7.269601499999997</v>
+        <v>-7.277661000000002</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.2396204611823131</v>
+        <v>0.199198393377358</v>
       </c>
       <c r="T47">
-        <v>1.656702077334868</v>
+        <v>1.626774642219991</v>
       </c>
       <c r="U47">
         <v>0.2388</v>
       </c>
       <c r="V47">
-        <v>-0.2031174465699557</v>
+        <v>-0.2029533775501092</v>
       </c>
       <c r="W47">
-        <v>0.2873044462409055</v>
+        <v>0.2872652665589661</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5045,7 +5104,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>-0.8124697862798227</v>
+        <v>-0.8118135102004369</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5056,25 +5115,25 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.2630782544586796</v>
+        <v>0.2408284863090817</v>
       </c>
       <c r="C48">
-        <v>-1.084793433472917</v>
+        <v>-7.412672994435738</v>
       </c>
       <c r="D48">
-        <v>55.81720656652708</v>
+        <v>49.53532700556426</v>
       </c>
       <c r="E48">
-        <v>56.902</v>
+        <v>56.948</v>
       </c>
       <c r="F48">
-        <v>56.902</v>
+        <v>56.948</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -5089,37 +5148,37 @@
         <v>-10.8</v>
       </c>
       <c r="M48">
-        <v>13.5881976</v>
+        <v>13.5991824</v>
       </c>
       <c r="N48">
-        <v>-24.3881976</v>
+        <v>-24.3991824</v>
       </c>
       <c r="O48">
-        <v>-6.0970494</v>
+        <v>-6.0997956</v>
       </c>
       <c r="P48">
-        <v>-18.2911482</v>
+        <v>-18.2993868</v>
       </c>
       <c r="Q48">
-        <v>-7.491148200000001</v>
+        <v>-7.4993868</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.2433393586116151</v>
+        <v>0.2021687339954572</v>
       </c>
       <c r="T48">
-        <v>1.687381745433661</v>
+        <v>1.656900098557399</v>
       </c>
       <c r="U48">
         <v>0.2388</v>
       </c>
       <c r="V48">
-        <v>-0.1987018499053914</v>
+        <v>-0.1985413476033677</v>
       </c>
       <c r="W48">
-        <v>0.2862500017574075</v>
+        <v>0.2862116738076843</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5127,7 +5186,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>-0.7948073996215657</v>
+        <v>-0.7941653904134709</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5138,25 +5197,25 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.2650782544586796</v>
+        <v>0.2428284863090817</v>
       </c>
       <c r="C49">
-        <v>-2.815143593876591</v>
+        <v>-9.136245650506162</v>
       </c>
       <c r="D49">
-        <v>55.32385640612341</v>
+        <v>49.04975434949384</v>
       </c>
       <c r="E49">
-        <v>58.139</v>
+        <v>58.186</v>
       </c>
       <c r="F49">
-        <v>58.139</v>
+        <v>58.186</v>
       </c>
       <c r="G49">
         <v>0</v>
       </c>
       <c r="H49">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -5171,37 +5230,37 @@
         <v>-10.8</v>
       </c>
       <c r="M49">
-        <v>13.8835932</v>
+        <v>13.8948168</v>
       </c>
       <c r="N49">
-        <v>-24.6835932</v>
+        <v>-24.6948168</v>
       </c>
       <c r="O49">
-        <v>-6.170898300000001</v>
+        <v>-6.1737042</v>
       </c>
       <c r="P49">
-        <v>-18.5126949</v>
+        <v>-18.5211126</v>
       </c>
       <c r="Q49">
-        <v>-7.712694900000002</v>
+        <v>-7.721112600000001</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.2471985917929664</v>
+        <v>0.2052511629387678</v>
       </c>
       <c r="T49">
-        <v>1.719219136856938</v>
+        <v>1.688162364567916</v>
       </c>
       <c r="U49">
         <v>0.2388</v>
       </c>
       <c r="V49">
-        <v>-0.1944741509712342</v>
+        <v>-0.1943170636118067</v>
       </c>
       <c r="W49">
-        <v>0.2852404272519308</v>
+        <v>0.2852029147904995</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5209,7 +5268,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>-0.7778966038849366</v>
+        <v>-0.7772682544472267</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5220,25 +5279,25 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.2670782544586796</v>
+        <v>0.2448284863090816</v>
       </c>
       <c r="C50">
-        <v>-4.536849038443044</v>
+        <v>-10.85039101494774</v>
       </c>
       <c r="D50">
-        <v>54.83915096155695</v>
+        <v>48.57360898505226</v>
       </c>
       <c r="E50">
-        <v>59.376</v>
+        <v>59.424</v>
       </c>
       <c r="F50">
-        <v>59.376</v>
+        <v>59.424</v>
       </c>
       <c r="G50">
         <v>0</v>
       </c>
       <c r="H50">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -5253,37 +5312,37 @@
         <v>-10.8</v>
       </c>
       <c r="M50">
-        <v>14.1789888</v>
+        <v>14.1904512</v>
       </c>
       <c r="N50">
-        <v>-24.9789888</v>
+        <v>-24.9904512</v>
       </c>
       <c r="O50">
-        <v>-6.244747200000001</v>
+        <v>-6.247612800000001</v>
       </c>
       <c r="P50">
-        <v>-18.7342416</v>
+        <v>-18.7428384</v>
       </c>
       <c r="Q50">
-        <v>-7.934241600000004</v>
+        <v>-7.942838400000003</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.2512062570197542</v>
+        <v>0.2084521468414364</v>
       </c>
       <c r="T50">
-        <v>1.752281043334957</v>
+        <v>1.720627025424991</v>
       </c>
       <c r="U50">
         <v>0.2388</v>
       </c>
       <c r="V50">
-        <v>-0.1904226061593335</v>
+        <v>-0.1902687914532274</v>
       </c>
       <c r="W50">
-        <v>0.2842729183508488</v>
+        <v>0.2842361873990307</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5291,7 +5350,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>-0.7616904246373339</v>
+        <v>-0.7610751658129096</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5302,25 +5361,25 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.2690782544586796</v>
+        <v>0.2468284863090817</v>
       </c>
       <c r="C51">
-        <v>-6.250135009000431</v>
+        <v>-12.55538099162703</v>
       </c>
       <c r="D51">
-        <v>54.36286499099957</v>
+        <v>48.10661900837297</v>
       </c>
       <c r="E51">
-        <v>60.613</v>
+        <v>60.662</v>
       </c>
       <c r="F51">
-        <v>60.613</v>
+        <v>60.662</v>
       </c>
       <c r="G51">
         <v>0</v>
       </c>
       <c r="H51">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -5335,37 +5394,37 @@
         <v>-10.8</v>
       </c>
       <c r="M51">
-        <v>14.4743844</v>
+        <v>14.4860856</v>
       </c>
       <c r="N51">
-        <v>-25.2743844</v>
+        <v>-25.2860856</v>
       </c>
       <c r="O51">
-        <v>-6.318596100000001</v>
+        <v>-6.3215214</v>
       </c>
       <c r="P51">
-        <v>-18.9557883</v>
+        <v>-18.9645642</v>
       </c>
       <c r="Q51">
-        <v>-8.155788300000001</v>
+        <v>-8.164564199999997</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.255371085588769</v>
+        <v>0.2117786595246018</v>
       </c>
       <c r="T51">
-        <v>1.786639495165054</v>
+        <v>1.754364810237246</v>
       </c>
       <c r="U51">
         <v>0.2388</v>
       </c>
       <c r="V51">
-        <v>-0.1865364305234287</v>
+        <v>-0.1863857548929574</v>
       </c>
       <c r="W51">
-        <v>0.2833448996089948</v>
+        <v>0.2833089182684383</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5373,7 +5432,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>-0.7461457220937149</v>
+        <v>-0.7455430195718296</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5384,25 +5443,25 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.2710782544586796</v>
+        <v>0.2488284863090817</v>
       </c>
       <c r="C52">
-        <v>-7.955218989721665</v>
+        <v>-14.25147712757288</v>
       </c>
       <c r="D52">
-        <v>53.89478101027834</v>
+        <v>47.64852287242712</v>
       </c>
       <c r="E52">
-        <v>61.85</v>
+        <v>61.9</v>
       </c>
       <c r="F52">
-        <v>61.85</v>
+        <v>61.9</v>
       </c>
       <c r="G52">
         <v>0</v>
       </c>
       <c r="H52">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -5417,37 +5476,37 @@
         <v>-10.8</v>
       </c>
       <c r="M52">
-        <v>14.76978</v>
+        <v>14.78172</v>
       </c>
       <c r="N52">
-        <v>-25.56978</v>
+        <v>-25.58172</v>
       </c>
       <c r="O52">
-        <v>-6.392445</v>
+        <v>-6.39543</v>
       </c>
       <c r="P52">
-        <v>-19.177335</v>
+        <v>-19.18629</v>
       </c>
       <c r="Q52">
-        <v>-8.377334999999999</v>
+        <v>-8.386289999999999</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.2597025073005443</v>
+        <v>0.2152382327150938</v>
       </c>
       <c r="T52">
-        <v>1.822372285068355</v>
+        <v>1.789452106441991</v>
       </c>
       <c r="U52">
         <v>0.2388</v>
       </c>
       <c r="V52">
-        <v>-0.1828057019129601</v>
+        <v>-0.1826580397950983</v>
       </c>
       <c r="W52">
-        <v>0.2824540016168149</v>
+        <v>0.2824187399030695</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5455,7 +5514,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>-0.7312228076518406</v>
+        <v>-0.730632159180393</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5466,25 +5525,25 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.2730782544586796</v>
+        <v>0.2508284863090817</v>
       </c>
       <c r="C53">
-        <v>-9.652311038254361</v>
+        <v>-15.93893110144099</v>
       </c>
       <c r="D53">
-        <v>53.43468896174564</v>
+        <v>47.19906889855901</v>
       </c>
       <c r="E53">
-        <v>63.087</v>
+        <v>63.138</v>
       </c>
       <c r="F53">
-        <v>63.087</v>
+        <v>63.138</v>
       </c>
       <c r="G53">
         <v>0</v>
       </c>
       <c r="H53">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -5499,37 +5558,37 @@
         <v>-10.8</v>
       </c>
       <c r="M53">
-        <v>15.0651756</v>
+        <v>15.0773544</v>
       </c>
       <c r="N53">
-        <v>-25.8651756</v>
+        <v>-25.8773544</v>
       </c>
       <c r="O53">
-        <v>-6.4662939</v>
+        <v>-6.4693386</v>
       </c>
       <c r="P53">
-        <v>-19.3988817</v>
+        <v>-19.4080158</v>
       </c>
       <c r="Q53">
-        <v>-8.5988817</v>
+        <v>-8.6080158</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.2642107217352493</v>
+        <v>0.2188390129745856</v>
       </c>
       <c r="T53">
-        <v>1.859563556192199</v>
+        <v>1.825971537185705</v>
       </c>
       <c r="U53">
         <v>0.2388</v>
       </c>
       <c r="V53">
-        <v>-0.179221276385255</v>
+        <v>-0.1790765096030375</v>
       </c>
       <c r="W53">
-        <v>0.2815980408007989</v>
+        <v>0.2815634704932054</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5537,7 +5596,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>-0.7168851055410199</v>
+        <v>-0.71630603841215</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5548,25 +5607,25 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.2750782544586796</v>
+        <v>0.2528284863090817</v>
       </c>
       <c r="C54">
-        <v>-11.3416141000335</v>
+        <v>-17.61798518459138</v>
       </c>
       <c r="D54">
-        <v>52.9823858999665</v>
+        <v>46.75801481540863</v>
       </c>
       <c r="E54">
-        <v>64.324</v>
+        <v>64.376</v>
       </c>
       <c r="F54">
-        <v>64.324</v>
+        <v>64.376</v>
       </c>
       <c r="G54">
         <v>0</v>
       </c>
       <c r="H54">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -5581,37 +5640,37 @@
         <v>-10.8</v>
       </c>
       <c r="M54">
-        <v>15.3605712</v>
+        <v>15.3729888</v>
       </c>
       <c r="N54">
-        <v>-26.1605712</v>
+        <v>-26.1729888</v>
       </c>
       <c r="O54">
-        <v>-6.5401428</v>
+        <v>-6.543247200000001</v>
       </c>
       <c r="P54">
-        <v>-19.6204284</v>
+        <v>-19.6297416</v>
       </c>
       <c r="Q54">
-        <v>-8.820428400000001</v>
+        <v>-8.829741600000002</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.2689067784380671</v>
+        <v>0.2225898257448894</v>
       </c>
       <c r="T54">
-        <v>1.89830446361287</v>
+        <v>1.864012610877074</v>
       </c>
       <c r="U54">
         <v>0.2388</v>
       </c>
       <c r="V54">
-        <v>-0.1757747133778463</v>
+        <v>-0.1756327305722099</v>
       </c>
       <c r="W54">
-        <v>0.2807750015546297</v>
+        <v>0.2807410960606437</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5619,7 +5678,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>-0.7030988535113849</v>
+        <v>-0.7025309222888394</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5630,25 +5689,25 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.2770782544586796</v>
+        <v>0.2548284863090817</v>
       </c>
       <c r="C55">
-        <v>-13.02332430676497</v>
+        <v>-19.28887267655399</v>
       </c>
       <c r="D55">
-        <v>52.53767569323504</v>
+        <v>46.32512732344601</v>
       </c>
       <c r="E55">
-        <v>65.56100000000001</v>
+        <v>65.614</v>
       </c>
       <c r="F55">
-        <v>65.56100000000001</v>
+        <v>65.614</v>
       </c>
       <c r="G55">
         <v>0</v>
       </c>
       <c r="H55">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -5663,37 +5722,37 @@
         <v>-10.8</v>
       </c>
       <c r="M55">
-        <v>15.6559668</v>
+        <v>15.6686232</v>
       </c>
       <c r="N55">
-        <v>-26.4559668</v>
+        <v>-26.4686232</v>
       </c>
       <c r="O55">
-        <v>-6.613991700000001</v>
+        <v>-6.617155800000001</v>
       </c>
       <c r="P55">
-        <v>-19.8419751</v>
+        <v>-19.8514674</v>
       </c>
       <c r="Q55">
-        <v>-9.041975100000002</v>
+        <v>-9.051467400000003</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.2738026673410047</v>
+        <v>0.2265002475692488</v>
       </c>
       <c r="T55">
-        <v>1.938693920285484</v>
+        <v>1.903672453661692</v>
       </c>
       <c r="U55">
         <v>0.2388</v>
       </c>
       <c r="V55">
-        <v>-0.1724582093518492</v>
+        <v>-0.1723189054670738</v>
       </c>
       <c r="W55">
-        <v>0.2799830203932216</v>
+        <v>0.2799497546255372</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5701,7 +5760,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>-0.6898328374073965</v>
+        <v>-0.6892756218682954</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5712,25 +5771,25 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.2790782544586796</v>
+        <v>0.2568284863090817</v>
       </c>
       <c r="C56">
-        <v>-14.69763126000214</v>
+        <v>-20.95181831652669</v>
       </c>
       <c r="D56">
-        <v>52.10036873999786</v>
+        <v>45.90018168347331</v>
       </c>
       <c r="E56">
-        <v>66.798</v>
+        <v>66.852</v>
       </c>
       <c r="F56">
-        <v>66.798</v>
+        <v>66.852</v>
       </c>
       <c r="G56">
         <v>0</v>
       </c>
       <c r="H56">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -5745,37 +5804,37 @@
         <v>-10.8</v>
       </c>
       <c r="M56">
-        <v>15.9513624</v>
+        <v>15.9642576</v>
       </c>
       <c r="N56">
-        <v>-26.7513624</v>
+        <v>-26.7642576</v>
       </c>
       <c r="O56">
-        <v>-6.6878406</v>
+        <v>-6.6910644</v>
       </c>
       <c r="P56">
-        <v>-20.0635218</v>
+        <v>-20.0731932</v>
       </c>
       <c r="Q56">
-        <v>-9.263521799999999</v>
+        <v>-9.273193199999998</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.2789114209788526</v>
+        <v>0.2305806877337977</v>
       </c>
       <c r="T56">
-        <v>1.98083944029169</v>
+        <v>1.945056637436946</v>
       </c>
       <c r="U56">
         <v>0.2388</v>
       </c>
       <c r="V56">
-        <v>-0.1692645388082964</v>
+        <v>-0.169127814625091</v>
       </c>
       <c r="W56">
-        <v>0.2792203718674212</v>
+        <v>0.2791877221324717</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5783,7 +5842,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>-0.6770581552331856</v>
+        <v>-0.6765112585003639</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5794,25 +5853,25 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.2810782544586796</v>
+        <v>0.2588284863090817</v>
       </c>
       <c r="C57">
-        <v>-16.36471830067698</v>
+        <v>-22.60703867243092</v>
       </c>
       <c r="D57">
-        <v>51.67028169932303</v>
+        <v>45.48296132756908</v>
       </c>
       <c r="E57">
-        <v>68.03500000000001</v>
+        <v>68.09</v>
       </c>
       <c r="F57">
-        <v>68.03500000000001</v>
+        <v>68.09</v>
       </c>
       <c r="G57">
         <v>0</v>
       </c>
       <c r="H57">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -5827,37 +5886,37 @@
         <v>-10.8</v>
       </c>
       <c r="M57">
-        <v>16.246758</v>
+        <v>16.259892</v>
       </c>
       <c r="N57">
-        <v>-27.046758</v>
+        <v>-27.059892</v>
       </c>
       <c r="O57">
-        <v>-6.761689500000001</v>
+        <v>-6.764973</v>
       </c>
       <c r="P57">
-        <v>-20.2850685</v>
+        <v>-20.294919</v>
       </c>
       <c r="Q57">
-        <v>-9.485068500000001</v>
+        <v>-9.494918999999999</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.2842472303339382</v>
+        <v>0.2348424807945487</v>
       </c>
       <c r="T57">
-        <v>2.024858094520395</v>
+        <v>1.988280118268879</v>
       </c>
       <c r="U57">
         <v>0.2388</v>
       </c>
       <c r="V57">
-        <v>-0.1661870017390546</v>
+        <v>-0.1660527634500893</v>
       </c>
       <c r="W57">
-        <v>0.2784854560152862</v>
+        <v>0.2784533999118814</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5865,7 +5924,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>-0.6647480069562184</v>
+        <v>-0.6642110538003574</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5876,25 +5935,25 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2830782544586796</v>
+        <v>0.2608284863090816</v>
       </c>
       <c r="C58">
-        <v>-18.02476276539058</v>
+        <v>-24.25474250894001</v>
       </c>
       <c r="D58">
-        <v>51.24723723460943</v>
+        <v>45.07325749105999</v>
       </c>
       <c r="E58">
-        <v>69.27200000000001</v>
+        <v>69.328</v>
       </c>
       <c r="F58">
-        <v>69.27200000000001</v>
+        <v>69.328</v>
       </c>
       <c r="G58">
         <v>0</v>
       </c>
       <c r="H58">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -5909,37 +5968,37 @@
         <v>-10.8</v>
       </c>
       <c r="M58">
-        <v>16.5421536</v>
+        <v>16.5555264</v>
       </c>
       <c r="N58">
-        <v>-27.3421536</v>
+        <v>-27.3555264</v>
       </c>
       <c r="O58">
-        <v>-6.835538400000001</v>
+        <v>-6.838881600000001</v>
       </c>
       <c r="P58">
-        <v>-20.5066152</v>
+        <v>-20.5166448</v>
       </c>
       <c r="Q58">
-        <v>-9.706615200000002</v>
+        <v>-9.716644800000001</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.2898255764778913</v>
+        <v>0.2392979917216975</v>
       </c>
       <c r="T58">
-        <v>2.070877596668585</v>
+        <v>2.033468302774989</v>
       </c>
       <c r="U58">
         <v>0.2388</v>
       </c>
       <c r="V58">
-        <v>-0.1632193767080001</v>
+        <v>-0.1630875355313377</v>
       </c>
       <c r="W58">
-        <v>0.2777767871578705</v>
+        <v>0.2777453034848835</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -5947,7 +6006,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>-0.6528775068320003</v>
+        <v>-0.652350142125351</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -5958,25 +6017,25 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2850782544586796</v>
+        <v>0.2628284863090817</v>
       </c>
       <c r="C59">
-        <v>-19.67793623021598</v>
+        <v>-25.89513113579417</v>
       </c>
       <c r="D59">
-        <v>50.83106376978404</v>
+        <v>44.67086886420584</v>
       </c>
       <c r="E59">
-        <v>70.50900000000001</v>
+        <v>70.566</v>
       </c>
       <c r="F59">
-        <v>70.50900000000001</v>
+        <v>70.566</v>
       </c>
       <c r="G59">
         <v>0</v>
       </c>
       <c r="H59">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -5991,37 +6050,37 @@
         <v>-10.8</v>
       </c>
       <c r="M59">
-        <v>16.83754920000001</v>
+        <v>16.8511608</v>
       </c>
       <c r="N59">
-        <v>-27.63754920000001</v>
+        <v>-27.6511608</v>
       </c>
       <c r="O59">
-        <v>-6.909387300000001</v>
+        <v>-6.912790200000001</v>
       </c>
       <c r="P59">
-        <v>-20.7281619</v>
+        <v>-20.7383706</v>
       </c>
       <c r="Q59">
-        <v>-9.928161900000003</v>
+        <v>-9.938370600000002</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.2956633805820283</v>
+        <v>0.2439607357152254</v>
       </c>
       <c r="T59">
-        <v>2.119037540777157</v>
+        <v>2.080758263304641</v>
       </c>
       <c r="U59">
         <v>0.2388</v>
       </c>
       <c r="V59">
-        <v>-0.1603558788710176</v>
+        <v>-0.1602263506974546</v>
       </c>
       <c r="W59">
-        <v>0.277092983874399</v>
+        <v>0.2770620525465522</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6029,7 +6088,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>-0.6414235154840704</v>
+        <v>-0.6409054027898184</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6040,25 +6099,25 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.2870782544586796</v>
+        <v>0.2648284863090817</v>
       </c>
       <c r="C60">
-        <v>-21.32440474271707</v>
+        <v>-27.52839873762306</v>
       </c>
       <c r="D60">
-        <v>50.42159525728292</v>
+        <v>44.27560126237693</v>
       </c>
       <c r="E60">
-        <v>71.746</v>
+        <v>71.80399999999999</v>
       </c>
       <c r="F60">
-        <v>71.746</v>
+        <v>71.80399999999999</v>
       </c>
       <c r="G60">
         <v>0</v>
       </c>
       <c r="H60">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -6073,37 +6132,37 @@
         <v>-10.8</v>
       </c>
       <c r="M60">
-        <v>17.1329448</v>
+        <v>17.1467952</v>
       </c>
       <c r="N60">
-        <v>-27.9329448</v>
+        <v>-27.9467952</v>
       </c>
       <c r="O60">
-        <v>-6.9832362</v>
+        <v>-6.9866988</v>
       </c>
       <c r="P60">
-        <v>-20.9497086</v>
+        <v>-20.9600964</v>
       </c>
       <c r="Q60">
-        <v>-10.1497086</v>
+        <v>-10.1600964</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.3017791753577909</v>
+        <v>0.2488455151370164</v>
       </c>
       <c r="T60">
-        <v>2.169490815557565</v>
+        <v>2.130300126716655</v>
       </c>
       <c r="U60">
         <v>0.2388</v>
       </c>
       <c r="V60">
-        <v>-0.1575911223387587</v>
+        <v>-0.1574638274095675</v>
       </c>
       <c r="W60">
-        <v>0.2764327600144956</v>
+        <v>0.2764023619854047</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6111,7 +6170,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>-0.6303644893550349</v>
+        <v>-0.62985530963827</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6122,25 +6181,25 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.2890782544586796</v>
+        <v>0.2668284863090816</v>
       </c>
       <c r="C61">
-        <v>-22.96432904284326</v>
+        <v>-29.15473268641192</v>
       </c>
       <c r="D61">
-        <v>50.01867095715674</v>
+        <v>43.88726731358807</v>
       </c>
       <c r="E61">
-        <v>72.983</v>
+        <v>73.04199999999999</v>
       </c>
       <c r="F61">
-        <v>72.983</v>
+        <v>73.04199999999999</v>
       </c>
       <c r="G61">
         <v>0</v>
       </c>
       <c r="H61">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -6155,37 +6214,37 @@
         <v>-10.8</v>
       </c>
       <c r="M61">
-        <v>17.4283404</v>
+        <v>17.4424296</v>
       </c>
       <c r="N61">
-        <v>-28.2283404</v>
+        <v>-28.2424296</v>
       </c>
       <c r="O61">
-        <v>-7.057085100000001</v>
+        <v>-7.060607399999999</v>
       </c>
       <c r="P61">
-        <v>-21.1712553</v>
+        <v>-21.1818222</v>
       </c>
       <c r="Q61">
-        <v>-10.3712553</v>
+        <v>-10.3818222</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.3081933015860297</v>
+        <v>0.2539685764818218</v>
       </c>
       <c r="T61">
-        <v>2.222405225693115</v>
+        <v>2.182258666392671</v>
       </c>
       <c r="U61">
         <v>0.2388</v>
       </c>
       <c r="V61">
-        <v>-0.1549200863669153</v>
+        <v>-0.1547949489788969</v>
       </c>
       <c r="W61">
-        <v>0.2757949166244194</v>
+        <v>0.2757650338161606</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6193,7 +6252,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>-0.6196803454676614</v>
+        <v>-0.6191797959155876</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6204,25 +6263,25 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.2910782544586796</v>
+        <v>0.2688284863090817</v>
       </c>
       <c r="C62">
-        <v>-24.5978647733166</v>
+        <v>-30.77431383766655</v>
       </c>
       <c r="D62">
-        <v>49.6221352266834</v>
+        <v>43.50568616233345</v>
       </c>
       <c r="E62">
-        <v>74.22</v>
+        <v>74.28</v>
       </c>
       <c r="F62">
-        <v>74.22</v>
+        <v>74.28</v>
       </c>
       <c r="G62">
         <v>0</v>
       </c>
       <c r="H62">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -6237,37 +6296,37 @@
         <v>-10.8</v>
       </c>
       <c r="M62">
-        <v>17.723736</v>
+        <v>17.738064</v>
       </c>
       <c r="N62">
-        <v>-28.523736</v>
+        <v>-28.538064</v>
       </c>
       <c r="O62">
-        <v>-7.130934000000001</v>
+        <v>-7.134516000000001</v>
       </c>
       <c r="P62">
-        <v>-21.392802</v>
+        <v>-21.403548</v>
       </c>
       <c r="Q62">
-        <v>-10.592802</v>
+        <v>-10.603548</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.3149281341256804</v>
+        <v>0.2593477908938673</v>
       </c>
       <c r="T62">
-        <v>2.277965356335443</v>
+        <v>2.236815133052488</v>
       </c>
       <c r="U62">
         <v>0.2388</v>
       </c>
       <c r="V62">
-        <v>-0.1523380849274668</v>
+        <v>-0.1522150331625819</v>
       </c>
       <c r="W62">
-        <v>0.275178334680679</v>
+        <v>0.2751489499192246</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6275,7 +6334,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>-0.609352339709867</v>
+        <v>-0.6088601326503276</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6286,25 +6345,25 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.2930782544586796</v>
+        <v>0.2708284863090816</v>
       </c>
       <c r="C63">
-        <v>-26.22516268009059</v>
+        <v>-32.38731681126161</v>
       </c>
       <c r="D63">
-        <v>49.2318373199094</v>
+        <v>43.1306831887384</v>
       </c>
       <c r="E63">
-        <v>75.45699999999999</v>
+        <v>75.518</v>
       </c>
       <c r="F63">
-        <v>75.45699999999999</v>
+        <v>75.518</v>
       </c>
       <c r="G63">
         <v>0</v>
       </c>
       <c r="H63">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -6319,37 +6378,37 @@
         <v>-10.8</v>
       </c>
       <c r="M63">
-        <v>18.0191316</v>
+        <v>18.0336984</v>
       </c>
       <c r="N63">
-        <v>-28.8191316</v>
+        <v>-28.8336984</v>
       </c>
       <c r="O63">
-        <v>-7.2047829</v>
+        <v>-7.208424600000001</v>
       </c>
       <c r="P63">
-        <v>-21.6143487</v>
+        <v>-21.6252738</v>
       </c>
       <c r="Q63">
-        <v>-10.8143487</v>
+        <v>-10.8252738</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.3220083426930056</v>
+        <v>0.2650028624552485</v>
       </c>
       <c r="T63">
-        <v>2.336374724446609</v>
+        <v>2.294169367233321</v>
       </c>
       <c r="U63">
         <v>0.2388</v>
       </c>
       <c r="V63">
-        <v>-0.1498407392729182</v>
+        <v>-0.1497197047500805</v>
       </c>
       <c r="W63">
-        <v>0.2745819685383729</v>
+        <v>0.2745530654943192</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6357,7 +6416,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>-0.5993629570916725</v>
+        <v>-0.5988788190003222</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6368,25 +6427,25 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.2950782544586796</v>
+        <v>0.2728284863090817</v>
       </c>
       <c r="C64">
-        <v>-27.84636880342244</v>
+        <v>-33.99391025788825</v>
       </c>
       <c r="D64">
-        <v>48.84763119657757</v>
+        <v>42.76208974211175</v>
       </c>
       <c r="E64">
-        <v>76.694</v>
+        <v>76.756</v>
       </c>
       <c r="F64">
-        <v>76.694</v>
+        <v>76.756</v>
       </c>
       <c r="G64">
         <v>0</v>
       </c>
       <c r="H64">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -6401,37 +6460,37 @@
         <v>-10.8</v>
       </c>
       <c r="M64">
-        <v>18.3145272</v>
+        <v>18.3293328</v>
       </c>
       <c r="N64">
-        <v>-29.1145272</v>
+        <v>-29.1293328</v>
       </c>
       <c r="O64">
-        <v>-7.2786318</v>
+        <v>-7.2823332</v>
       </c>
       <c r="P64">
-        <v>-21.8358954</v>
+        <v>-21.8469996</v>
       </c>
       <c r="Q64">
-        <v>-11.0358954</v>
+        <v>-11.0469996</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.3294611938165057</v>
+        <v>0.2709555693619656</v>
       </c>
       <c r="T64">
-        <v>2.397858269826783</v>
+        <v>2.354542245318409</v>
       </c>
       <c r="U64">
         <v>0.2388</v>
       </c>
       <c r="V64">
-        <v>-0.147423953155613</v>
+        <v>-0.1473048708024986</v>
       </c>
       <c r="W64">
-        <v>0.2740048400135604</v>
+        <v>0.2739764031476367</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6439,7 +6498,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>-0.5896958126224521</v>
+        <v>-0.5892194832099944</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6450,25 +6509,25 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.2970782544586796</v>
+        <v>0.2748284863090816</v>
       </c>
       <c r="C65">
-        <v>-29.46162466006786</v>
+        <v>-35.59425711195495</v>
       </c>
       <c r="D65">
-        <v>48.46937533993214</v>
+        <v>42.39974288804505</v>
       </c>
       <c r="E65">
-        <v>77.931</v>
+        <v>77.994</v>
       </c>
       <c r="F65">
-        <v>77.931</v>
+        <v>77.994</v>
       </c>
       <c r="G65">
         <v>0</v>
       </c>
       <c r="H65">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -6483,37 +6542,37 @@
         <v>-10.8</v>
       </c>
       <c r="M65">
-        <v>18.6099228</v>
+        <v>18.6249672</v>
       </c>
       <c r="N65">
-        <v>-29.4099228</v>
+        <v>-29.4249672</v>
       </c>
       <c r="O65">
-        <v>-7.3524807</v>
+        <v>-7.3562418</v>
       </c>
       <c r="P65">
-        <v>-22.0574421</v>
+        <v>-22.0687254</v>
       </c>
       <c r="Q65">
-        <v>-11.2574421</v>
+        <v>-11.2687254</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.3373169017574923</v>
+        <v>0.2772300442095862</v>
       </c>
       <c r="T65">
-        <v>2.462665250092371</v>
+        <v>2.418178522218906</v>
       </c>
       <c r="U65">
         <v>0.2388</v>
       </c>
       <c r="V65">
-        <v>-0.1450838904071112</v>
+        <v>-0.144966698250078</v>
       </c>
       <c r="W65">
-        <v>0.2734460330292182</v>
+        <v>0.2734180475421186</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6521,7 +6580,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>-0.5803355616284449</v>
+        <v>-0.5798667930003121</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6532,25 +6591,25 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.2990782544586796</v>
+        <v>0.2768284863090817</v>
       </c>
       <c r="C66">
-        <v>-31.07106741707604</v>
+        <v>-37.18851483173888</v>
       </c>
       <c r="D66">
-        <v>48.09693258292397</v>
+        <v>42.04348516826112</v>
       </c>
       <c r="E66">
-        <v>79.16800000000001</v>
+        <v>79.232</v>
       </c>
       <c r="F66">
-        <v>79.16800000000001</v>
+        <v>79.232</v>
       </c>
       <c r="G66">
         <v>0</v>
       </c>
       <c r="H66">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -6565,37 +6624,37 @@
         <v>-10.8</v>
       </c>
       <c r="M66">
-        <v>18.9053184</v>
+        <v>18.9206016</v>
       </c>
       <c r="N66">
-        <v>-29.7053184</v>
+        <v>-29.7206016</v>
       </c>
       <c r="O66">
-        <v>-7.426329600000001</v>
+        <v>-7.4301504</v>
       </c>
       <c r="P66">
-        <v>-22.2789888</v>
+        <v>-22.2904512</v>
       </c>
       <c r="Q66">
-        <v>-11.4789888</v>
+        <v>-11.4904512</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.3456090379174228</v>
+        <v>0.2838531009931859</v>
       </c>
       <c r="T66">
-        <v>2.531072618150493</v>
+        <v>2.485350147836098</v>
       </c>
       <c r="U66">
         <v>0.2388</v>
       </c>
       <c r="V66">
-        <v>-0.1428169546195001</v>
+        <v>-0.1427015935899205</v>
       </c>
       <c r="W66">
-        <v>0.2729046887631367</v>
+        <v>0.272877140549273</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6603,7 +6662,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>-0.5712678184780002</v>
+        <v>-0.5708063743596821</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6614,25 +6673,25 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.3010782544586796</v>
+        <v>0.2788284863090817</v>
       </c>
       <c r="C67">
-        <v>-32.67483005763266</v>
+        <v>-38.77683562753077</v>
       </c>
       <c r="D67">
-        <v>47.73016994236734</v>
+        <v>41.69316437246923</v>
       </c>
       <c r="E67">
-        <v>80.405</v>
+        <v>80.47</v>
       </c>
       <c r="F67">
-        <v>80.405</v>
+        <v>80.47</v>
       </c>
       <c r="G67">
         <v>0</v>
       </c>
       <c r="H67">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -6647,37 +6706,37 @@
         <v>-10.8</v>
       </c>
       <c r="M67">
-        <v>19.200714</v>
+        <v>19.216236</v>
       </c>
       <c r="N67">
-        <v>-30.000714</v>
+        <v>-30.016236</v>
       </c>
       <c r="O67">
-        <v>-7.500178500000001</v>
+        <v>-7.504059000000001</v>
       </c>
       <c r="P67">
-        <v>-22.5005355</v>
+        <v>-22.512177</v>
       </c>
       <c r="Q67">
-        <v>-11.7005355</v>
+        <v>-11.712177</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.3543750104293491</v>
+        <v>0.2908546181644198</v>
       </c>
       <c r="T67">
-        <v>2.603388978669078</v>
+        <v>2.556360152059987</v>
       </c>
       <c r="U67">
         <v>0.2388</v>
       </c>
       <c r="V67">
-        <v>-0.140619770702277</v>
+        <v>-0.1405061844577679</v>
       </c>
       <c r="W67">
-        <v>0.2723800012437038</v>
+        <v>0.272352876848515</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6685,7 +6744,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>-0.562479082809108</v>
+        <v>-0.5620247378310717</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6696,25 +6755,25 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.3030782544586796</v>
+        <v>0.2808284863090817</v>
       </c>
       <c r="C68">
-        <v>-34.27304153937287</v>
+        <v>-40.3593666784685</v>
       </c>
       <c r="D68">
-        <v>47.36895846062714</v>
+        <v>41.34863332153149</v>
       </c>
       <c r="E68">
-        <v>81.64200000000001</v>
+        <v>81.708</v>
       </c>
       <c r="F68">
-        <v>81.64200000000001</v>
+        <v>81.708</v>
       </c>
       <c r="G68">
         <v>0</v>
       </c>
       <c r="H68">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -6729,37 +6788,37 @@
         <v>-10.8</v>
       </c>
       <c r="M68">
-        <v>19.4961096</v>
+        <v>19.5118704</v>
       </c>
       <c r="N68">
-        <v>-30.2961096</v>
+        <v>-30.3118704</v>
       </c>
       <c r="O68">
-        <v>-7.574027400000001</v>
+        <v>-7.5779676</v>
       </c>
       <c r="P68">
-        <v>-22.7220822</v>
+        <v>-22.7339028</v>
       </c>
       <c r="Q68">
-        <v>-11.9220822</v>
+        <v>-11.9339028</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.3636566283831534</v>
+        <v>0.2982679892869027</v>
       </c>
       <c r="T68">
-        <v>2.67995924274758</v>
+        <v>2.631547215355869</v>
       </c>
       <c r="U68">
         <v>0.2388</v>
       </c>
       <c r="V68">
-        <v>-0.1384891681158789</v>
+        <v>-0.1383773028750745</v>
       </c>
       <c r="W68">
-        <v>0.2718712133460719</v>
+        <v>0.2718444999265678</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6767,7 +6826,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>-0.5539566724635154</v>
+        <v>-0.5535092115002977</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6778,25 +6837,25 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.3050782544586796</v>
+        <v>0.2828284863090816</v>
       </c>
       <c r="C69">
-        <v>-35.86582694555952</v>
+        <v>-41.93625033870774</v>
       </c>
       <c r="D69">
-        <v>47.01317305444049</v>
+        <v>41.00974966129226</v>
       </c>
       <c r="E69">
-        <v>82.879</v>
+        <v>82.946</v>
       </c>
       <c r="F69">
-        <v>82.879</v>
+        <v>82.946</v>
       </c>
       <c r="G69">
         <v>0</v>
       </c>
       <c r="H69">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -6811,37 +6870,37 @@
         <v>-10.8</v>
       </c>
       <c r="M69">
-        <v>19.7915052</v>
+        <v>19.8075048</v>
       </c>
       <c r="N69">
-        <v>-30.5915052</v>
+        <v>-30.6075048</v>
       </c>
       <c r="O69">
-        <v>-7.647876300000001</v>
+        <v>-7.6518762</v>
       </c>
       <c r="P69">
-        <v>-22.9436289</v>
+        <v>-22.9556286</v>
       </c>
       <c r="Q69">
-        <v>-12.1436289</v>
+        <v>-12.1556286</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.3735007686371885</v>
+        <v>0.3061306556289301</v>
       </c>
       <c r="T69">
-        <v>2.761170128891447</v>
+        <v>2.711291070366653</v>
       </c>
       <c r="U69">
         <v>0.2388</v>
       </c>
       <c r="V69">
-        <v>-0.1364221656066866</v>
+        <v>-0.136311969996342</v>
       </c>
       <c r="W69">
-        <v>0.2713776131468768</v>
+        <v>0.2713512984351265</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6849,7 +6908,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>-0.5456886624267465</v>
+        <v>-0.5452478799853679</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6860,25 +6919,25 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.3070782544586796</v>
+        <v>0.2848284863090817</v>
       </c>
       <c r="C70">
-        <v>-37.45330762949943</v>
+        <v>-43.50762433353673</v>
       </c>
       <c r="D70">
-        <v>46.66269237050059</v>
+        <v>40.67637566646327</v>
       </c>
       <c r="E70">
-        <v>84.11600000000001</v>
+        <v>84.184</v>
       </c>
       <c r="F70">
-        <v>84.11600000000001</v>
+        <v>84.184</v>
       </c>
       <c r="G70">
         <v>0</v>
       </c>
       <c r="H70">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -6893,37 +6952,37 @@
         <v>-10.8</v>
       </c>
       <c r="M70">
-        <v>20.08690080000001</v>
+        <v>20.1031392</v>
       </c>
       <c r="N70">
-        <v>-30.88690080000001</v>
+        <v>-30.9031392</v>
       </c>
       <c r="O70">
-        <v>-7.721725200000002</v>
+        <v>-7.7257848</v>
       </c>
       <c r="P70">
-        <v>-23.1651756</v>
+        <v>-23.1773544</v>
       </c>
       <c r="Q70">
-        <v>-12.3651756</v>
+        <v>-12.3773544</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.3839601676571006</v>
+        <v>0.3144847386173342</v>
       </c>
       <c r="T70">
-        <v>2.847456695419305</v>
+        <v>2.796018916315611</v>
       </c>
       <c r="U70">
         <v>0.2388</v>
       </c>
       <c r="V70">
-        <v>-0.1344159572889412</v>
+        <v>-0.1343073822022781</v>
       </c>
       <c r="W70">
-        <v>0.2708985306005992</v>
+        <v>0.2708726028699041</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -6931,7 +6990,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>-0.5376638291557649</v>
+        <v>-0.5372295288091125</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -6942,25 +7001,25 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.3090782544586796</v>
+        <v>0.2868284863090817</v>
       </c>
       <c r="C71">
-        <v>-39.0356013525476</v>
+        <v>-45.07362194600271</v>
       </c>
       <c r="D71">
-        <v>46.31739864745241</v>
+        <v>40.3483780539973</v>
       </c>
       <c r="E71">
-        <v>85.35300000000001</v>
+        <v>85.42200000000001</v>
       </c>
       <c r="F71">
-        <v>85.35300000000001</v>
+        <v>85.42200000000001</v>
       </c>
       <c r="G71">
         <v>0</v>
       </c>
       <c r="H71">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -6975,37 +7034,37 @@
         <v>-10.8</v>
       </c>
       <c r="M71">
-        <v>20.3822964</v>
+        <v>20.39877360000001</v>
       </c>
       <c r="N71">
-        <v>-31.18229640000001</v>
+        <v>-31.19877360000001</v>
       </c>
       <c r="O71">
-        <v>-7.795574100000001</v>
+        <v>-7.799693400000002</v>
       </c>
       <c r="P71">
-        <v>-23.3867223</v>
+        <v>-23.3990802</v>
       </c>
       <c r="Q71">
-        <v>-12.5867223</v>
+        <v>-12.5990802</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.3950943666137813</v>
+        <v>0.3233777947017643</v>
       </c>
       <c r="T71">
-        <v>2.939310137207024</v>
+        <v>2.886213074906437</v>
       </c>
       <c r="U71">
         <v>0.2388</v>
       </c>
       <c r="V71">
-        <v>-0.1324678999369276</v>
+        <v>-0.1323608984022451</v>
       </c>
       <c r="W71">
-        <v>0.2704333345049383</v>
+        <v>0.2704077825384562</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7013,7 +7072,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>-0.5298715997477104</v>
+        <v>-0.5294435936089803</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7024,25 +7083,25 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.3110782544586796</v>
+        <v>0.2888284863090816</v>
       </c>
       <c r="C72">
-        <v>-40.61282241602942</v>
+        <v>-46.63437219458132</v>
       </c>
       <c r="D72">
-        <v>45.97717758397059</v>
+        <v>40.02562780541869</v>
       </c>
       <c r="E72">
-        <v>86.59</v>
+        <v>86.66000000000001</v>
       </c>
       <c r="F72">
-        <v>86.59</v>
+        <v>86.66000000000001</v>
       </c>
       <c r="G72">
         <v>0</v>
       </c>
       <c r="H72">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -7057,37 +7116,37 @@
         <v>-10.8</v>
       </c>
       <c r="M72">
-        <v>20.677692</v>
+        <v>20.694408</v>
       </c>
       <c r="N72">
-        <v>-31.477692</v>
+        <v>-31.494408</v>
       </c>
       <c r="O72">
-        <v>-7.869423</v>
+        <v>-7.873602000000001</v>
       </c>
       <c r="P72">
-        <v>-23.608269</v>
+        <v>-23.620806</v>
       </c>
       <c r="Q72">
-        <v>-12.808269</v>
+        <v>-12.820806</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.4069708455009073</v>
+        <v>0.3328637211918231</v>
       </c>
       <c r="T72">
-        <v>3.037287141780592</v>
+        <v>2.982420177403318</v>
       </c>
       <c r="U72">
         <v>0.2388</v>
       </c>
       <c r="V72">
-        <v>-0.1305755013664001</v>
+        <v>-0.1304700284250702</v>
       </c>
       <c r="W72">
-        <v>0.2699814297262964</v>
+        <v>0.2699562427879068</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7095,7 +7154,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>-0.5223020054656002</v>
+        <v>-0.5218801137002806</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7106,25 +7165,25 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.3130782544586797</v>
+        <v>0.2908284863090817</v>
       </c>
       <c r="C73">
-        <v>-42.18508178739089</v>
+        <v>-48.19000000238661</v>
       </c>
       <c r="D73">
-        <v>45.64191821260911</v>
+        <v>39.70799999761338</v>
       </c>
       <c r="E73">
-        <v>87.827</v>
+        <v>87.898</v>
       </c>
       <c r="F73">
-        <v>87.827</v>
+        <v>87.898</v>
       </c>
       <c r="G73">
         <v>0</v>
       </c>
       <c r="H73">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -7139,37 +7198,37 @@
         <v>-10.8</v>
       </c>
       <c r="M73">
-        <v>20.9730876</v>
+        <v>20.9900424</v>
       </c>
       <c r="N73">
-        <v>-31.7730876</v>
+        <v>-31.7900424</v>
       </c>
       <c r="O73">
-        <v>-7.9432719</v>
+        <v>-7.9475106</v>
       </c>
       <c r="P73">
-        <v>-23.8298157</v>
+        <v>-23.8425318</v>
       </c>
       <c r="Q73">
-        <v>-13.0298157</v>
+        <v>-13.0425318</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.4196663918974902</v>
+        <v>0.3430038495087824</v>
       </c>
       <c r="T73">
-        <v>3.142021181152336</v>
+        <v>3.08526225248619</v>
       </c>
       <c r="U73">
         <v>0.2388</v>
       </c>
       <c r="V73">
-        <v>-0.1287364097978592</v>
+        <v>-0.1286324223909143</v>
       </c>
       <c r="W73">
-        <v>0.2695422546597288</v>
+        <v>0.2695174224669504</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7177,7 +7236,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>-0.5149456391914369</v>
+        <v>-0.5145296895636571</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7188,25 +7247,25 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.3150782544586797</v>
+        <v>0.2928284863090817</v>
       </c>
       <c r="C74">
-        <v>-43.75248722086981</v>
+        <v>-49.74062635838748</v>
       </c>
       <c r="D74">
-        <v>45.31151277913018</v>
+        <v>39.39537364161252</v>
       </c>
       <c r="E74">
-        <v>89.06399999999999</v>
+        <v>89.136</v>
       </c>
       <c r="F74">
-        <v>89.06399999999999</v>
+        <v>89.136</v>
       </c>
       <c r="G74">
         <v>0</v>
       </c>
       <c r="H74">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -7221,37 +7280,37 @@
         <v>-10.8</v>
       </c>
       <c r="M74">
-        <v>21.2684832</v>
+        <v>21.2856768</v>
       </c>
       <c r="N74">
-        <v>-32.0684832</v>
+        <v>-32.0856768</v>
       </c>
       <c r="O74">
-        <v>-8.017120800000001</v>
+        <v>-8.0214192</v>
       </c>
       <c r="P74">
-        <v>-24.0513624</v>
+        <v>-24.0642576</v>
       </c>
       <c r="Q74">
-        <v>-13.2513624</v>
+        <v>-13.2642576</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.4332687630366863</v>
+        <v>0.3538682727055247</v>
       </c>
       <c r="T74">
-        <v>3.254236223336348</v>
+        <v>3.195450190074983</v>
       </c>
       <c r="U74">
         <v>0.2388</v>
       </c>
       <c r="V74">
-        <v>-0.1269484041062223</v>
+        <v>-0.1268458609688183</v>
       </c>
       <c r="W74">
-        <v>0.2691152789005659</v>
+        <v>0.2690907915993538</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7259,7 +7318,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>-0.5077936164248895</v>
+        <v>-0.5073834438752729</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7270,25 +7329,25 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.3170782544586795</v>
+        <v>0.2948284863090816</v>
       </c>
       <c r="C75">
-        <v>-45.31514337296312</v>
+        <v>-51.28636847106827</v>
       </c>
       <c r="D75">
-        <v>44.98585662703688</v>
+        <v>39.08763152893172</v>
       </c>
       <c r="E75">
-        <v>90.301</v>
+        <v>90.374</v>
       </c>
       <c r="F75">
-        <v>90.301</v>
+        <v>90.374</v>
       </c>
       <c r="G75">
         <v>0</v>
       </c>
       <c r="H75">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -7303,37 +7362,37 @@
         <v>-10.8</v>
       </c>
       <c r="M75">
-        <v>21.5638788</v>
+        <v>21.5813112</v>
       </c>
       <c r="N75">
-        <v>-32.3638788</v>
+        <v>-32.3813112</v>
       </c>
       <c r="O75">
-        <v>-8.0909697</v>
+        <v>-8.0953278</v>
       </c>
       <c r="P75">
-        <v>-24.2729091</v>
+        <v>-24.2859834</v>
       </c>
       <c r="Q75">
-        <v>-13.4729091</v>
+        <v>-13.4859834</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.4478787172232302</v>
+        <v>0.3655374679909145</v>
       </c>
       <c r="T75">
-        <v>3.374763490867323</v>
+        <v>3.313800197114797</v>
       </c>
       <c r="U75">
         <v>0.2388</v>
       </c>
       <c r="V75">
-        <v>-0.1252093848718905</v>
+        <v>-0.1251082464349988</v>
       </c>
       <c r="W75">
-        <v>0.2687000011074074</v>
+        <v>0.2686758492486777</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7341,7 +7400,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>-0.5008375394875619</v>
+        <v>-0.5004329857399954</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7352,25 +7411,25 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.3190782544586796</v>
+        <v>0.2968284863090817</v>
       </c>
       <c r="C76">
-        <v>-46.87315191295079</v>
+        <v>-52.82733991494297</v>
       </c>
       <c r="D76">
-        <v>44.66484808704921</v>
+        <v>38.78466008505703</v>
       </c>
       <c r="E76">
-        <v>91.538</v>
+        <v>91.61199999999999</v>
       </c>
       <c r="F76">
-        <v>91.538</v>
+        <v>91.61199999999999</v>
       </c>
       <c r="G76">
         <v>0</v>
       </c>
       <c r="H76">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -7385,37 +7444,37 @@
         <v>-10.8</v>
       </c>
       <c r="M76">
-        <v>21.8592744</v>
+        <v>21.8769456</v>
       </c>
       <c r="N76">
-        <v>-32.6592744</v>
+        <v>-32.6769456</v>
       </c>
       <c r="O76">
-        <v>-8.1648186</v>
+        <v>-8.169236399999999</v>
       </c>
       <c r="P76">
-        <v>-24.4944558</v>
+        <v>-24.5077092</v>
       </c>
       <c r="Q76">
-        <v>-13.6944558</v>
+        <v>-13.7077092</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.4636125140395083</v>
+        <v>0.3781042936828727</v>
       </c>
       <c r="T76">
-        <v>3.504562086669912</v>
+        <v>3.441254050849981</v>
       </c>
       <c r="U76">
         <v>0.2388</v>
       </c>
       <c r="V76">
-        <v>-0.1235173661574055</v>
+        <v>-0.1234175944561475</v>
       </c>
       <c r="W76">
-        <v>0.2682959470383884</v>
+        <v>0.2682721215561281</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7423,7 +7482,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>-0.494069464629622</v>
+        <v>-0.4936703778245899</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7434,25 +7493,25 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.3210782544586796</v>
+        <v>0.2988284863090817</v>
       </c>
       <c r="C77">
-        <v>-48.42661162872099</v>
+        <v>-54.36365077030792</v>
       </c>
       <c r="D77">
-        <v>44.34838837127901</v>
+        <v>38.48634922969207</v>
       </c>
       <c r="E77">
-        <v>92.77500000000001</v>
+        <v>92.84999999999999</v>
       </c>
       <c r="F77">
-        <v>92.77500000000001</v>
+        <v>92.84999999999999</v>
       </c>
       <c r="G77">
         <v>0</v>
       </c>
       <c r="H77">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -7467,37 +7526,37 @@
         <v>-10.8</v>
       </c>
       <c r="M77">
-        <v>22.15467</v>
+        <v>22.17258</v>
       </c>
       <c r="N77">
-        <v>-32.95467000000001</v>
+        <v>-32.97258</v>
       </c>
       <c r="O77">
-        <v>-8.238667500000002</v>
+        <v>-8.243145</v>
       </c>
       <c r="P77">
-        <v>-24.71600250000001</v>
+        <v>-24.729435</v>
       </c>
       <c r="Q77">
-        <v>-13.9160025</v>
+        <v>-13.929435</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.4806050146010887</v>
+        <v>0.3916764654301877</v>
       </c>
       <c r="T77">
-        <v>3.644744570136709</v>
+        <v>3.578904212883981</v>
       </c>
       <c r="U77">
         <v>0.2388</v>
       </c>
       <c r="V77">
-        <v>-0.1218704679419734</v>
+        <v>-0.1217720265300655</v>
       </c>
       <c r="W77">
-        <v>0.2679026677445432</v>
+        <v>0.2678791599353796</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7505,7 +7564,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>-0.4874818717678937</v>
+        <v>-0.4870881061202621</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7516,25 +7575,25 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.3230782544586797</v>
+        <v>0.3008284863090817</v>
       </c>
       <c r="C78">
-        <v>-49.97561852812825</v>
+        <v>-55.89540775659447</v>
       </c>
       <c r="D78">
-        <v>44.03638147187175</v>
+        <v>38.19259224340553</v>
       </c>
       <c r="E78">
-        <v>94.012</v>
+        <v>94.08799999999999</v>
       </c>
       <c r="F78">
-        <v>94.012</v>
+        <v>94.08799999999999</v>
       </c>
       <c r="G78">
         <v>0</v>
       </c>
       <c r="H78">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -7549,37 +7608,37 @@
         <v>-10.8</v>
       </c>
       <c r="M78">
-        <v>22.4500656</v>
+        <v>22.4682144</v>
       </c>
       <c r="N78">
-        <v>-33.2500656</v>
+        <v>-33.26821440000001</v>
       </c>
       <c r="O78">
-        <v>-8.3125164</v>
+        <v>-8.317053600000001</v>
       </c>
       <c r="P78">
-        <v>-24.9375492</v>
+        <v>-24.9511608</v>
       </c>
       <c r="Q78">
-        <v>-14.1375492</v>
+        <v>-14.1511608</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.4990135568761341</v>
+        <v>0.4063796514897789</v>
       </c>
       <c r="T78">
-        <v>3.79660892722574</v>
+        <v>3.728025221754148</v>
       </c>
       <c r="U78">
         <v>0.2388</v>
       </c>
       <c r="V78">
-        <v>-0.1202669091532632</v>
+        <v>-0.120169763023091</v>
       </c>
       <c r="W78">
-        <v>0.2675197379057993</v>
+        <v>0.2674965394099141</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7587,7 +7646,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>-0.4810676366130529</v>
+        <v>-0.4806790520923641</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7598,25 +7657,25 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.3250782544586797</v>
+        <v>0.3028284863090817</v>
       </c>
       <c r="C79">
-        <v>-51.52026593610299</v>
+        <v>-57.42271435966074</v>
       </c>
       <c r="D79">
-        <v>43.72873406389702</v>
+        <v>37.90328564033926</v>
       </c>
       <c r="E79">
-        <v>95.24900000000001</v>
+        <v>95.32599999999999</v>
       </c>
       <c r="F79">
-        <v>95.24900000000001</v>
+        <v>95.32599999999999</v>
       </c>
       <c r="G79">
         <v>0</v>
       </c>
       <c r="H79">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -7631,37 +7690,37 @@
         <v>-10.8</v>
       </c>
       <c r="M79">
-        <v>22.7454612</v>
+        <v>22.7638488</v>
       </c>
       <c r="N79">
-        <v>-33.54546120000001</v>
+        <v>-33.5638488</v>
       </c>
       <c r="O79">
-        <v>-8.386365300000001</v>
+        <v>-8.390962200000001</v>
       </c>
       <c r="P79">
-        <v>-25.1590959</v>
+        <v>-25.1728866</v>
       </c>
       <c r="Q79">
-        <v>-14.3590959</v>
+        <v>-14.3728866</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.5190228419577052</v>
+        <v>0.4223613754675953</v>
       </c>
       <c r="T79">
-        <v>3.961678880583381</v>
+        <v>3.890113274873893</v>
       </c>
       <c r="U79">
         <v>0.2388</v>
       </c>
       <c r="V79">
-        <v>-0.1187050012421819</v>
+        <v>-0.1186091167500638</v>
       </c>
       <c r="W79">
-        <v>0.2671467542966331</v>
+        <v>0.2671238570799153</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7669,7 +7728,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>-0.4748200049687274</v>
+        <v>-0.4744364670002554</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7680,25 +7739,25 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.3270782544586796</v>
+        <v>0.3048284863090817</v>
       </c>
       <c r="C80">
-        <v>-53.06064458771865</v>
+        <v>-58.94567095334149</v>
       </c>
       <c r="D80">
-        <v>43.42535541228136</v>
+        <v>37.61832904665852</v>
       </c>
       <c r="E80">
-        <v>96.486</v>
+        <v>96.56400000000001</v>
       </c>
       <c r="F80">
-        <v>96.486</v>
+        <v>96.56400000000001</v>
       </c>
       <c r="G80">
         <v>0</v>
       </c>
       <c r="H80">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -7713,37 +7772,37 @@
         <v>-10.8</v>
       </c>
       <c r="M80">
-        <v>23.0408568</v>
+        <v>23.0594832</v>
       </c>
       <c r="N80">
-        <v>-33.8408568</v>
+        <v>-33.8594832</v>
       </c>
       <c r="O80">
-        <v>-8.460214200000001</v>
+        <v>-8.4648708</v>
       </c>
       <c r="P80">
-        <v>-25.3806426</v>
+        <v>-25.3946124</v>
       </c>
       <c r="Q80">
-        <v>-14.5806426</v>
+        <v>-14.5946124</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.5408511529557827</v>
+        <v>0.439795983443395</v>
       </c>
       <c r="T80">
-        <v>4.14175519333717</v>
+        <v>4.066936605549978</v>
       </c>
       <c r="U80">
         <v>0.2388</v>
       </c>
       <c r="V80">
-        <v>-0.1171831422518975</v>
+        <v>-0.1170884870481399</v>
       </c>
       <c r="W80">
-        <v>0.2667833343697531</v>
+        <v>0.2667607307070958</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7751,7 +7810,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>-0.4687325690075901</v>
+        <v>-0.4683539481925596</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7762,25 +7821,25 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.3290782544586796</v>
+        <v>0.3068284863090817</v>
       </c>
       <c r="C81">
-        <v>-54.59684271741158</v>
+        <v>-60.46437491555601</v>
       </c>
       <c r="D81">
-        <v>43.12615728258843</v>
+        <v>37.33762508444399</v>
       </c>
       <c r="E81">
-        <v>97.72300000000001</v>
+        <v>97.80200000000001</v>
       </c>
       <c r="F81">
-        <v>97.72300000000001</v>
+        <v>97.80200000000001</v>
       </c>
       <c r="G81">
         <v>0</v>
       </c>
       <c r="H81">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -7795,37 +7854,37 @@
         <v>-10.8</v>
       </c>
       <c r="M81">
-        <v>23.3362524</v>
+        <v>23.3551176</v>
       </c>
       <c r="N81">
-        <v>-34.1362524</v>
+        <v>-34.1551176</v>
       </c>
       <c r="O81">
-        <v>-8.534063100000001</v>
+        <v>-8.538779400000001</v>
       </c>
       <c r="P81">
-        <v>-25.6021893</v>
+        <v>-25.6163382</v>
       </c>
       <c r="Q81">
-        <v>-14.8021893</v>
+        <v>-14.8163382</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.564758350715582</v>
+        <v>0.4588910302740331</v>
       </c>
       <c r="T81">
-        <v>4.338981631115131</v>
+        <v>4.260600253433312</v>
       </c>
       <c r="U81">
         <v>0.2388</v>
       </c>
       <c r="V81">
-        <v>-0.1156998113373165</v>
+        <v>-0.1156063543006951</v>
       </c>
       <c r="W81">
-        <v>0.2664291149473512</v>
+        <v>0.266406797407006</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7833,7 +7892,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>-0.462799245349266</v>
+        <v>-0.4624254172027804</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7844,25 +7903,25 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.3310782544586797</v>
+        <v>0.3088284863090817</v>
       </c>
       <c r="C82">
-        <v>-56.12894614453764</v>
+        <v>-61.9789207392563</v>
       </c>
       <c r="D82">
-        <v>42.83105385546236</v>
+        <v>37.0610792607437</v>
       </c>
       <c r="E82">
-        <v>98.96000000000001</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="F82">
-        <v>98.96000000000001</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="G82">
         <v>0</v>
       </c>
       <c r="H82">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -7877,37 +7936,37 @@
         <v>-10.8</v>
       </c>
       <c r="M82">
-        <v>23.631648</v>
+        <v>23.650752</v>
       </c>
       <c r="N82">
-        <v>-34.431648</v>
+        <v>-34.45075200000001</v>
       </c>
       <c r="O82">
-        <v>-8.607912000000001</v>
+        <v>-8.612688000000002</v>
       </c>
       <c r="P82">
-        <v>-25.823736</v>
+        <v>-25.83806400000001</v>
       </c>
       <c r="Q82">
-        <v>-15.023736</v>
+        <v>-15.03806400000001</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.5910562682513609</v>
+        <v>0.4798955817877347</v>
       </c>
       <c r="T82">
-        <v>4.555930712670888</v>
+        <v>4.473630266104977</v>
       </c>
       <c r="U82">
         <v>0.2388</v>
       </c>
       <c r="V82">
-        <v>-0.1142535636956001</v>
+        <v>-0.1141612748719364</v>
       </c>
       <c r="W82">
-        <v>0.2660837510105094</v>
+        <v>0.2660617124394185</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -7915,7 +7974,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>-0.4570142547824003</v>
+        <v>-0.4566450994877458</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -7926,25 +7985,25 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3330782544586796</v>
+        <v>0.3108284863090817</v>
       </c>
       <c r="C83">
-        <v>-57.65703835544018</v>
+        <v>-63.48940013848094</v>
       </c>
       <c r="D83">
-        <v>42.53996164455982</v>
+        <v>36.78859986151907</v>
       </c>
       <c r="E83">
-        <v>100.197</v>
+        <v>100.278</v>
       </c>
       <c r="F83">
-        <v>100.197</v>
+        <v>100.278</v>
       </c>
       <c r="G83">
         <v>0</v>
       </c>
       <c r="H83">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -7959,37 +8018,37 @@
         <v>-10.8</v>
       </c>
       <c r="M83">
-        <v>23.9270436</v>
+        <v>23.9463864</v>
       </c>
       <c r="N83">
-        <v>-34.7270436</v>
+        <v>-34.74638640000001</v>
       </c>
       <c r="O83">
-        <v>-8.6817609</v>
+        <v>-8.686596600000001</v>
       </c>
       <c r="P83">
-        <v>-26.0452827</v>
+        <v>-26.0597898</v>
       </c>
       <c r="Q83">
-        <v>-15.2452827</v>
+        <v>-15.2597898</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.6201223876330115</v>
+        <v>0.5031111387239312</v>
       </c>
       <c r="T83">
-        <v>4.795716539653566</v>
+        <v>4.709084490636818</v>
       </c>
       <c r="U83">
         <v>0.2388</v>
       </c>
       <c r="V83">
-        <v>-0.1128430258721976</v>
+        <v>-0.1127518764167273</v>
       </c>
       <c r="W83">
-        <v>0.2657469145782808</v>
+        <v>0.2657251480883145</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -7997,7 +8056,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>-0.4513721034887903</v>
+        <v>-0.4510075056669094</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8008,25 +8067,25 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3350782544586797</v>
+        <v>0.3128284863090817</v>
       </c>
       <c r="C84">
-        <v>-59.18120058219412</v>
+        <v>-64.99590214976473</v>
       </c>
       <c r="D84">
-        <v>42.25279941780589</v>
+        <v>36.52009785023528</v>
       </c>
       <c r="E84">
-        <v>101.434</v>
+        <v>101.516</v>
       </c>
       <c r="F84">
-        <v>101.434</v>
+        <v>101.516</v>
       </c>
       <c r="G84">
         <v>0</v>
       </c>
       <c r="H84">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -8041,37 +8100,37 @@
         <v>-10.8</v>
       </c>
       <c r="M84">
-        <v>24.2224392</v>
+        <v>24.2420208</v>
       </c>
       <c r="N84">
-        <v>-35.02243920000001</v>
+        <v>-35.0420208</v>
       </c>
       <c r="O84">
-        <v>-8.755609800000002</v>
+        <v>-8.760505200000001</v>
       </c>
       <c r="P84">
-        <v>-26.26682940000001</v>
+        <v>-26.2815156</v>
       </c>
       <c r="Q84">
-        <v>-15.46682940000001</v>
+        <v>-15.4815156</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.6524180758348457</v>
+        <v>0.5289062019863719</v>
       </c>
       <c r="T84">
-        <v>5.062145236300987</v>
+        <v>4.970700295672198</v>
       </c>
       <c r="U84">
         <v>0.2388</v>
       </c>
       <c r="V84">
-        <v>-0.1114668914103415</v>
+        <v>-0.1113768535335965</v>
       </c>
       <c r="W84">
-        <v>0.2654182936687896</v>
+        <v>0.2653967926238229</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8079,7 +8138,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>-0.4458675656413662</v>
+        <v>-0.445507414134386</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8090,25 +8149,25 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3370782544586797</v>
+        <v>0.3148284863090817</v>
       </c>
       <c r="C85">
-        <v>-60.70151187818173</v>
+        <v>-66.49851322913963</v>
       </c>
       <c r="D85">
-        <v>41.96948812181827</v>
+        <v>36.25548677086037</v>
       </c>
       <c r="E85">
-        <v>102.671</v>
+        <v>102.754</v>
       </c>
       <c r="F85">
-        <v>102.671</v>
+        <v>102.754</v>
       </c>
       <c r="G85">
         <v>0</v>
       </c>
       <c r="H85">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -8123,37 +8182,37 @@
         <v>-10.8</v>
       </c>
       <c r="M85">
-        <v>24.5178348</v>
+        <v>24.5376552</v>
       </c>
       <c r="N85">
-        <v>-35.3178348</v>
+        <v>-35.3376552</v>
       </c>
       <c r="O85">
-        <v>-8.8294587</v>
+        <v>-8.8344138</v>
       </c>
       <c r="P85">
-        <v>-26.4883761</v>
+        <v>-26.5032414</v>
       </c>
       <c r="Q85">
-        <v>-15.6883761</v>
+        <v>-15.7032414</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.6885132567663073</v>
+        <v>0.5577359785738056</v>
       </c>
       <c r="T85">
-        <v>5.359918485495164</v>
+        <v>5.263094430711739</v>
       </c>
       <c r="U85">
         <v>0.2388</v>
       </c>
       <c r="V85">
-        <v>-0.1101239168150362</v>
+        <v>-0.1100349637319869</v>
       </c>
       <c r="W85">
-        <v>0.2650975913354307</v>
+        <v>0.2650763493391985</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8161,7 +8220,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>-0.4404956672601448</v>
+        <v>-0.4401398549279474</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8172,25 +8231,25 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.3390782544586796</v>
+        <v>0.3168284863090817</v>
       </c>
       <c r="C86">
-        <v>-62.21804919064864</v>
+        <v>-67.99731734494922</v>
       </c>
       <c r="D86">
-        <v>41.68995080935136</v>
+        <v>35.99468265505077</v>
       </c>
       <c r="E86">
-        <v>103.908</v>
+        <v>103.992</v>
       </c>
       <c r="F86">
-        <v>103.908</v>
+        <v>103.992</v>
       </c>
       <c r="G86">
         <v>0</v>
       </c>
       <c r="H86">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I86">
         <v>0</v>
@@ -8205,37 +8264,37 @@
         <v>-10.8</v>
       </c>
       <c r="M86">
-        <v>24.8132304</v>
+        <v>24.8332896</v>
       </c>
       <c r="N86">
-        <v>-35.61323040000001</v>
+        <v>-35.6332896</v>
       </c>
       <c r="O86">
-        <v>-8.903307600000002</v>
+        <v>-8.908322399999999</v>
       </c>
       <c r="P86">
-        <v>-26.7099228</v>
+        <v>-26.7249672</v>
       </c>
       <c r="Q86">
-        <v>-15.9099228</v>
+        <v>-15.9249672</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.7291203353142011</v>
+        <v>0.5901694772346682</v>
       </c>
       <c r="T86">
-        <v>5.694913390838608</v>
+        <v>5.592037832631219</v>
       </c>
       <c r="U86">
         <v>0.2388</v>
       </c>
       <c r="V86">
-        <v>-0.1088129178053334</v>
+        <v>-0.1087250236875585</v>
       </c>
       <c r="W86">
-        <v>0.2647845247719136</v>
+        <v>0.264763535656589</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8243,7 +8302,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>-0.4352516712213337</v>
+        <v>-0.4349000947502339</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8254,25 +8313,25 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.3410782544586797</v>
+        <v>0.3188284863090816</v>
       </c>
       <c r="C87">
-        <v>-63.73088743037918</v>
+        <v>-69.49239606668556</v>
       </c>
       <c r="D87">
-        <v>41.41411256962081</v>
+        <v>35.73760393331444</v>
       </c>
       <c r="E87">
-        <v>105.145</v>
+        <v>105.23</v>
       </c>
       <c r="F87">
-        <v>105.145</v>
+        <v>105.23</v>
       </c>
       <c r="G87">
         <v>0</v>
       </c>
       <c r="H87">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -8287,37 +8346,37 @@
         <v>-10.8</v>
       </c>
       <c r="M87">
-        <v>25.108626</v>
+        <v>25.128924</v>
       </c>
       <c r="N87">
-        <v>-35.908626</v>
+        <v>-35.92892399999999</v>
       </c>
       <c r="O87">
-        <v>-8.9771565</v>
+        <v>-8.982230999999999</v>
       </c>
       <c r="P87">
-        <v>-26.9314695</v>
+        <v>-26.946693</v>
       </c>
       <c r="Q87">
-        <v>-16.1314695</v>
+        <v>-16.146693</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.7751416910018145</v>
+        <v>0.6269274423836459</v>
       </c>
       <c r="T87">
-        <v>6.074574283561183</v>
+        <v>5.964840354806634</v>
       </c>
       <c r="U87">
         <v>0.2388</v>
       </c>
       <c r="V87">
-        <v>-0.107532765831153</v>
+        <v>-0.1074459057618225</v>
       </c>
       <c r="W87">
-        <v>0.2644788244804794</v>
+        <v>0.2644580822959232</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8325,7 +8384,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>-0.4301310633246118</v>
+        <v>-0.42978362304729</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8336,25 +8395,25 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.3430782544586796</v>
+        <v>0.3208284863090817</v>
       </c>
       <c r="C88">
-        <v>-65.24009953862398</v>
+        <v>-70.98382865004631</v>
       </c>
       <c r="D88">
-        <v>41.14190046137603</v>
+        <v>35.48417134995368</v>
       </c>
       <c r="E88">
-        <v>106.382</v>
+        <v>106.468</v>
       </c>
       <c r="F88">
-        <v>106.382</v>
+        <v>106.468</v>
       </c>
       <c r="G88">
         <v>0</v>
       </c>
       <c r="H88">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -8369,37 +8428,37 @@
         <v>-10.8</v>
       </c>
       <c r="M88">
-        <v>25.4040216</v>
+        <v>25.4245584</v>
       </c>
       <c r="N88">
-        <v>-36.2040216</v>
+        <v>-36.2245584</v>
       </c>
       <c r="O88">
-        <v>-9.051005400000001</v>
+        <v>-9.0561396</v>
       </c>
       <c r="P88">
-        <v>-27.1530162</v>
+        <v>-27.1684188</v>
       </c>
       <c r="Q88">
-        <v>-16.3530162</v>
+        <v>-16.3684188</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.8277375260733726</v>
+        <v>0.6689365454110494</v>
       </c>
       <c r="T88">
-        <v>6.508472446672695</v>
+        <v>6.390900380149967</v>
       </c>
       <c r="U88">
         <v>0.2388</v>
       </c>
       <c r="V88">
-        <v>-0.1062823848331163</v>
+        <v>-0.106196534764592</v>
       </c>
       <c r="W88">
-        <v>0.2641802334981482</v>
+        <v>0.2641597325017846</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8407,7 +8466,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>-0.4251295393324654</v>
+        <v>-0.424786139058368</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8418,25 +8477,25 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.3450782544586797</v>
+        <v>0.3228284863090816</v>
       </c>
       <c r="C89">
-        <v>-66.74575655140532</v>
+        <v>-72.47169211839814</v>
       </c>
       <c r="D89">
-        <v>40.87324344859469</v>
+        <v>35.23430788160186</v>
       </c>
       <c r="E89">
-        <v>107.619</v>
+        <v>107.706</v>
       </c>
       <c r="F89">
-        <v>107.619</v>
+        <v>107.706</v>
       </c>
       <c r="G89">
         <v>0</v>
       </c>
       <c r="H89">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -8451,37 +8510,37 @@
         <v>-10.8</v>
       </c>
       <c r="M89">
-        <v>25.6994172</v>
+        <v>25.7201928</v>
       </c>
       <c r="N89">
-        <v>-36.4994172</v>
+        <v>-36.5201928</v>
       </c>
       <c r="O89">
-        <v>-9.124854300000001</v>
+        <v>-9.130048200000001</v>
       </c>
       <c r="P89">
-        <v>-27.3745629</v>
+        <v>-27.3901446</v>
       </c>
       <c r="Q89">
-        <v>-16.5745629</v>
+        <v>-16.5901446</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.8884250280790169</v>
+        <v>0.7174085873657454</v>
       </c>
       <c r="T89">
-        <v>7.009124173339827</v>
+        <v>6.882508101699963</v>
       </c>
       <c r="U89">
         <v>0.2388</v>
       </c>
       <c r="V89">
-        <v>-0.1050607482258391</v>
+        <v>-0.1049758849397116</v>
       </c>
       <c r="W89">
-        <v>0.2638885066763304</v>
+        <v>0.2638682413236031</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8489,7 +8548,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>-0.4202429929033566</v>
+        <v>-0.4199035397588466</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8500,25 +8559,25 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.3470782544586797</v>
+        <v>0.3248284863090817</v>
       </c>
       <c r="C90">
-        <v>-68.24792766131942</v>
+        <v>-73.95606134082257</v>
       </c>
       <c r="D90">
-        <v>40.60807233868059</v>
+        <v>34.98793865917743</v>
       </c>
       <c r="E90">
-        <v>108.856</v>
+        <v>108.944</v>
       </c>
       <c r="F90">
-        <v>108.856</v>
+        <v>108.944</v>
       </c>
       <c r="G90">
         <v>0</v>
       </c>
       <c r="H90">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -8533,37 +8592,37 @@
         <v>-10.8</v>
       </c>
       <c r="M90">
-        <v>25.9948128</v>
+        <v>26.0158272</v>
       </c>
       <c r="N90">
-        <v>-36.7948128</v>
+        <v>-36.8158272</v>
       </c>
       <c r="O90">
-        <v>-9.198703200000001</v>
+        <v>-9.2039568</v>
       </c>
       <c r="P90">
-        <v>-27.5961096</v>
+        <v>-27.6118704</v>
       </c>
       <c r="Q90">
-        <v>-16.7961096</v>
+        <v>-16.8118704</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.9592271137522683</v>
+        <v>0.7739593029795577</v>
       </c>
       <c r="T90">
-        <v>7.593217854451479</v>
+        <v>7.456050443508295</v>
       </c>
       <c r="U90">
         <v>0.2388</v>
       </c>
       <c r="V90">
-        <v>-0.1038668760869092</v>
+        <v>-0.1037829771563058</v>
       </c>
       <c r="W90">
-        <v>0.263603410009554</v>
+        <v>0.2635833749449258</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8571,7 +8630,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>-0.4154675043476366</v>
+        <v>-0.4151319086252234</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8582,25 +8641,25 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.3490782544586796</v>
+        <v>0.3268284863090817</v>
       </c>
       <c r="C91">
-        <v>-69.74668027694841</v>
+        <v>-75.43700910691007</v>
       </c>
       <c r="D91">
-        <v>40.34631972305159</v>
+        <v>34.74499089308994</v>
       </c>
       <c r="E91">
-        <v>110.093</v>
+        <v>110.182</v>
       </c>
       <c r="F91">
-        <v>110.093</v>
+        <v>110.182</v>
       </c>
       <c r="G91">
         <v>0</v>
       </c>
       <c r="H91">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -8615,37 +8674,37 @@
         <v>-10.8</v>
       </c>
       <c r="M91">
-        <v>26.2902084</v>
+        <v>26.3114616</v>
       </c>
       <c r="N91">
-        <v>-37.0902084</v>
+        <v>-37.1114616</v>
       </c>
       <c r="O91">
-        <v>-9.2725521</v>
+        <v>-9.2778654</v>
       </c>
       <c r="P91">
-        <v>-27.8176563</v>
+        <v>-27.8335962</v>
       </c>
       <c r="Q91">
-        <v>-17.0176563</v>
+        <v>-17.0335962</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>1.042902305911565</v>
+        <v>0.8407919668867903</v>
       </c>
       <c r="T91">
-        <v>8.28351038667434</v>
+        <v>8.133873211099958</v>
       </c>
       <c r="U91">
         <v>0.2388</v>
       </c>
       <c r="V91">
-        <v>-0.1026998325353708</v>
+        <v>-0.1026168762893811</v>
       </c>
       <c r="W91">
-        <v>0.2633247200094466</v>
+        <v>0.2633049100579042</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8653,7 +8712,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>-0.4107993301414834</v>
+        <v>-0.4104675051575242</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8664,25 +8723,25 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.3510782544586796</v>
+        <v>0.3288284863090817</v>
       </c>
       <c r="C92">
-        <v>-71.24208007998939</v>
+        <v>-76.91460619845964</v>
       </c>
       <c r="D92">
-        <v>40.08791992001061</v>
+        <v>34.50539380154036</v>
       </c>
       <c r="E92">
-        <v>111.33</v>
+        <v>111.42</v>
       </c>
       <c r="F92">
-        <v>111.33</v>
+        <v>111.42</v>
       </c>
       <c r="G92">
         <v>0</v>
       </c>
       <c r="H92">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -8697,37 +8756,37 @@
         <v>-10.8</v>
       </c>
       <c r="M92">
-        <v>26.585604</v>
+        <v>26.607096</v>
       </c>
       <c r="N92">
-        <v>-37.385604</v>
+        <v>-37.407096</v>
       </c>
       <c r="O92">
-        <v>-9.346401</v>
+        <v>-9.351774000000001</v>
       </c>
       <c r="P92">
-        <v>-28.039203</v>
+        <v>-28.055322</v>
       </c>
       <c r="Q92">
-        <v>-17.239203</v>
+        <v>-17.255322</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>1.143312536502722</v>
+        <v>0.9209911635754693</v>
       </c>
       <c r="T92">
-        <v>9.111861425341775</v>
+        <v>8.947260532209954</v>
       </c>
       <c r="U92">
         <v>0.2388</v>
       </c>
       <c r="V92">
-        <v>-0.1015587232849779</v>
+        <v>-0.1014766887750546</v>
       </c>
       <c r="W92">
-        <v>0.2630522231204527</v>
+        <v>0.2630326332794831</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8735,7 +8794,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>-0.4062348931399113</v>
+        <v>-0.4059067551002185</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8746,25 +8805,25 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.3530782544586796</v>
+        <v>0.3308284863090817</v>
       </c>
       <c r="C93">
-        <v>-72.734191080202</v>
+        <v>-78.38892145823206</v>
       </c>
       <c r="D93">
-        <v>39.83280891979801</v>
+        <v>34.26907854176793</v>
       </c>
       <c r="E93">
-        <v>112.567</v>
+        <v>112.658</v>
       </c>
       <c r="F93">
-        <v>112.567</v>
+        <v>112.658</v>
       </c>
       <c r="G93">
         <v>0</v>
       </c>
       <c r="H93">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -8779,37 +8838,37 @@
         <v>-10.8</v>
       </c>
       <c r="M93">
-        <v>26.8809996</v>
+        <v>26.9027304</v>
       </c>
       <c r="N93">
-        <v>-37.68099960000001</v>
+        <v>-37.70273040000001</v>
       </c>
       <c r="O93">
-        <v>-9.420249900000002</v>
+        <v>-9.425682600000002</v>
       </c>
       <c r="P93">
-        <v>-28.26074970000001</v>
+        <v>-28.27704780000001</v>
       </c>
       <c r="Q93">
-        <v>-17.4607497</v>
+        <v>-17.4770478</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>1.266036151669691</v>
+        <v>1.019012403972744</v>
       </c>
       <c r="T93">
-        <v>10.12429047260197</v>
+        <v>9.941400591344395</v>
       </c>
       <c r="U93">
         <v>0.2388</v>
       </c>
       <c r="V93">
-        <v>-0.1004426933587693</v>
+        <v>-0.1003615603269771</v>
       </c>
       <c r="W93">
-        <v>0.2627857151740741</v>
+        <v>0.2627663406060822</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8817,7 +8876,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>-0.4017707734350773</v>
+        <v>-0.4014462413079083</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8828,25 +8887,25 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.3550782544586796</v>
+        <v>0.3328284863090816</v>
       </c>
       <c r="C94">
-        <v>-74.22307566827126</v>
+        <v>-79.86002185589723</v>
       </c>
       <c r="D94">
-        <v>39.58092433172875</v>
+        <v>34.03597814410276</v>
       </c>
       <c r="E94">
-        <v>113.804</v>
+        <v>113.896</v>
       </c>
       <c r="F94">
-        <v>113.804</v>
+        <v>113.896</v>
       </c>
       <c r="G94">
         <v>0</v>
       </c>
       <c r="H94">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -8861,37 +8920,37 @@
         <v>-10.8</v>
       </c>
       <c r="M94">
-        <v>27.1763952</v>
+        <v>27.1983648</v>
       </c>
       <c r="N94">
-        <v>-37.9763952</v>
+        <v>-37.9983648</v>
       </c>
       <c r="O94">
-        <v>-9.4940988</v>
+        <v>-9.499591200000001</v>
       </c>
       <c r="P94">
-        <v>-28.4822964</v>
+        <v>-28.4987736</v>
       </c>
       <c r="Q94">
-        <v>-17.6822964</v>
+        <v>-17.6987736</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>1.419440670628403</v>
+        <v>1.141538954469337</v>
       </c>
       <c r="T94">
-        <v>11.38982678167722</v>
+        <v>11.18407566526245</v>
       </c>
       <c r="U94">
         <v>0.2388</v>
       </c>
       <c r="V94">
-        <v>-0.09935092495269571</v>
+        <v>-0.09927067380168385</v>
       </c>
       <c r="W94">
-        <v>0.2625250008787037</v>
+        <v>0.2625058369038421</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -8899,7 +8958,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>-0.3974036998107828</v>
+        <v>-0.3970826952067354</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -8910,25 +8969,25 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.3570782544586796</v>
+        <v>0.3348284863090816</v>
       </c>
       <c r="C95">
-        <v>-75.70879466667755</v>
+        <v>-81.32797255130812</v>
       </c>
       <c r="D95">
-        <v>39.33220533332246</v>
+        <v>33.80602744869188</v>
       </c>
       <c r="E95">
-        <v>115.041</v>
+        <v>115.134</v>
       </c>
       <c r="F95">
-        <v>115.041</v>
+        <v>115.134</v>
       </c>
       <c r="G95">
         <v>0</v>
       </c>
       <c r="H95">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I95">
         <v>0</v>
@@ -8943,37 +9002,37 @@
         <v>-10.8</v>
       </c>
       <c r="M95">
-        <v>27.4717908</v>
+        <v>27.4939992</v>
       </c>
       <c r="N95">
-        <v>-38.27179080000001</v>
+        <v>-38.2939992</v>
       </c>
       <c r="O95">
-        <v>-9.567947700000001</v>
+        <v>-9.5734998</v>
       </c>
       <c r="P95">
-        <v>-28.7038431</v>
+        <v>-28.7204994</v>
       </c>
       <c r="Q95">
-        <v>-17.9038431</v>
+        <v>-17.9204994</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>1.616675052146747</v>
+        <v>1.2990730908221</v>
       </c>
       <c r="T95">
-        <v>13.0169448933454</v>
+        <v>12.78180076029994</v>
       </c>
       <c r="U95">
         <v>0.2388</v>
       </c>
       <c r="V95">
-        <v>-0.09828263543707531</v>
+        <v>-0.09820324720166573</v>
       </c>
       <c r="W95">
-        <v>0.2622698933423736</v>
+        <v>0.2622509354317578</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -8981,7 +9040,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>-0.3931305417483013</v>
+        <v>-0.3928129888066629</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -8992,25 +9051,25 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3590782544586797</v>
+        <v>0.3368284863090817</v>
       </c>
       <c r="C96">
-        <v>-77.19140737866013</v>
+        <v>-82.7928369552271</v>
       </c>
       <c r="D96">
-        <v>39.08659262133988</v>
+        <v>33.5791630447729</v>
       </c>
       <c r="E96">
-        <v>116.278</v>
+        <v>116.372</v>
       </c>
       <c r="F96">
-        <v>116.278</v>
+        <v>116.372</v>
       </c>
       <c r="G96">
         <v>0</v>
       </c>
       <c r="H96">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -9025,37 +9084,37 @@
         <v>-10.8</v>
       </c>
       <c r="M96">
-        <v>27.7671864</v>
+        <v>27.7896336</v>
       </c>
       <c r="N96">
-        <v>-38.5671864</v>
+        <v>-38.5896336</v>
       </c>
       <c r="O96">
-        <v>-9.641796600000001</v>
+        <v>-9.6474084</v>
       </c>
       <c r="P96">
-        <v>-28.9253898</v>
+        <v>-28.9422252</v>
       </c>
       <c r="Q96">
-        <v>-18.1253898</v>
+        <v>-18.1422252</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>1.879654227504538</v>
+        <v>1.509118605959117</v>
       </c>
       <c r="T96">
-        <v>15.18643570890297</v>
+        <v>14.9121008870166</v>
       </c>
       <c r="U96">
         <v>0.2388</v>
       </c>
       <c r="V96">
-        <v>-0.09723707548561708</v>
+        <v>-0.09715853180590334</v>
       </c>
       <c r="W96">
-        <v>0.2620202136259654</v>
+        <v>0.2620014573952498</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9063,7 +9122,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>-0.3889483019424682</v>
+        <v>-0.3886341272236131</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9074,25 +9133,25 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3610782544586797</v>
+        <v>0.3388284863090817</v>
       </c>
       <c r="C97">
-        <v>-78.67097163535809</v>
+        <v>-84.25467678762342</v>
       </c>
       <c r="D97">
-        <v>38.84402836464193</v>
+        <v>33.35532321237658</v>
       </c>
       <c r="E97">
-        <v>117.515</v>
+        <v>117.61</v>
       </c>
       <c r="F97">
-        <v>117.515</v>
+        <v>117.61</v>
       </c>
       <c r="G97">
         <v>0</v>
       </c>
       <c r="H97">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -9107,37 +9166,37 @@
         <v>-10.8</v>
       </c>
       <c r="M97">
-        <v>28.06258200000001</v>
+        <v>28.085268</v>
       </c>
       <c r="N97">
-        <v>-38.862582</v>
+        <v>-38.885268</v>
       </c>
       <c r="O97">
-        <v>-9.715645500000001</v>
+        <v>-9.721317000000001</v>
       </c>
       <c r="P97">
-        <v>-29.1469365</v>
+        <v>-29.163951</v>
       </c>
       <c r="Q97">
-        <v>-18.3469365</v>
+        <v>-18.363951</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>2.247825073005447</v>
+        <v>1.803182327150941</v>
       </c>
       <c r="T97">
-        <v>18.22372285068357</v>
+        <v>17.89452106441993</v>
       </c>
       <c r="U97">
         <v>0.2388</v>
       </c>
       <c r="V97">
-        <v>-0.09621352732261057</v>
+        <v>-0.09613581041847277</v>
       </c>
       <c r="W97">
-        <v>0.2617757903246394</v>
+        <v>0.2617572315279313</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9145,7 +9204,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>-0.3848541092904421</v>
+        <v>-0.384543241673891</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9156,25 +9215,25 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.3630782544586796</v>
+        <v>0.3408284863090817</v>
       </c>
       <c r="C98">
-        <v>-80.1475438412063</v>
+        <v>-85.71355213365447</v>
       </c>
       <c r="D98">
-        <v>38.6044561587937</v>
+        <v>33.13444786634553</v>
       </c>
       <c r="E98">
-        <v>118.752</v>
+        <v>118.848</v>
       </c>
       <c r="F98">
-        <v>118.752</v>
+        <v>118.848</v>
       </c>
       <c r="G98">
         <v>0</v>
       </c>
       <c r="H98">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -9189,37 +9248,37 @@
         <v>-10.8</v>
       </c>
       <c r="M98">
-        <v>28.3579776</v>
+        <v>28.3809024</v>
       </c>
       <c r="N98">
-        <v>-39.1579776</v>
+        <v>-39.1809024</v>
       </c>
       <c r="O98">
-        <v>-9.789494400000001</v>
+        <v>-9.7952256</v>
       </c>
       <c r="P98">
-        <v>-29.3684832</v>
+        <v>-29.3856768</v>
       </c>
       <c r="Q98">
-        <v>-18.5684832</v>
+        <v>-18.5856768</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>2.800081341256802</v>
+        <v>2.244277908938671</v>
       </c>
       <c r="T98">
-        <v>22.77965356335441</v>
+        <v>22.36815133052486</v>
       </c>
       <c r="U98">
         <v>0.2388</v>
       </c>
       <c r="V98">
-        <v>-0.09521130307966673</v>
+        <v>-0.09513439572661368</v>
       </c>
       <c r="W98">
-        <v>0.2615364591754244</v>
+        <v>0.2615180936995154</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9227,7 +9286,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>-0.380845212318667</v>
+        <v>-0.3805375829064548</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9238,25 +9297,25 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.3650782544586796</v>
+        <v>0.3428284863090816</v>
       </c>
       <c r="C99">
-        <v>-81.62117901766231</v>
+        <v>-87.16952149743744</v>
       </c>
       <c r="D99">
-        <v>38.36782098233769</v>
+        <v>32.91647850256256</v>
       </c>
       <c r="E99">
-        <v>119.989</v>
+        <v>120.086</v>
       </c>
       <c r="F99">
-        <v>119.989</v>
+        <v>120.086</v>
       </c>
       <c r="G99">
         <v>0</v>
       </c>
       <c r="H99">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -9271,37 +9330,37 @@
         <v>-10.8</v>
       </c>
       <c r="M99">
-        <v>28.6533732</v>
+        <v>28.6765368</v>
       </c>
       <c r="N99">
-        <v>-39.4533732</v>
+        <v>-39.47653680000001</v>
       </c>
       <c r="O99">
-        <v>-9.8633433</v>
+        <v>-9.869134200000001</v>
       </c>
       <c r="P99">
-        <v>-29.5900299</v>
+        <v>-29.6074026</v>
       </c>
       <c r="Q99">
-        <v>-18.7900299</v>
+        <v>-18.8074026</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>3.72050845500907</v>
+        <v>2.979437211918228</v>
       </c>
       <c r="T99">
-        <v>30.37287141780589</v>
+        <v>29.82420177403315</v>
       </c>
       <c r="U99">
         <v>0.2388</v>
       </c>
       <c r="V99">
-        <v>-0.09422974325410316</v>
+        <v>-0.09415362876035993</v>
       </c>
       <c r="W99">
-        <v>0.2613020626890798</v>
+        <v>0.261283886547974</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9309,7 +9368,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>-0.3769189730164126</v>
+        <v>-0.3766145150414399</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9320,25 +9379,25 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.3670782544586796</v>
+        <v>0.3448284863090817</v>
       </c>
       <c r="C100">
-        <v>-83.09193084533426</v>
+        <v>-88.62264185371251</v>
       </c>
       <c r="D100">
-        <v>38.13406915466574</v>
+        <v>32.7013581462875</v>
       </c>
       <c r="E100">
-        <v>121.226</v>
+        <v>121.324</v>
       </c>
       <c r="F100">
-        <v>121.226</v>
+        <v>121.324</v>
       </c>
       <c r="G100">
         <v>0</v>
       </c>
       <c r="H100">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I100">
         <v>0</v>
@@ -9353,37 +9412,37 @@
         <v>-10.8</v>
       </c>
       <c r="M100">
-        <v>28.9487688</v>
+        <v>28.9721712</v>
       </c>
       <c r="N100">
-        <v>-39.7487688</v>
+        <v>-39.7721712</v>
       </c>
       <c r="O100">
-        <v>-9.9371922</v>
+        <v>-9.943042800000001</v>
       </c>
       <c r="P100">
-        <v>-29.8115766</v>
+        <v>-29.8291284</v>
       </c>
       <c r="Q100">
-        <v>-19.0115766</v>
+        <v>-19.0291284</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>5.561362682513605</v>
+        <v>4.449755817877342</v>
       </c>
       <c r="T100">
-        <v>45.55930712670883</v>
+        <v>44.73630266104973</v>
       </c>
       <c r="U100">
         <v>0.2388</v>
       </c>
       <c r="V100">
-        <v>-0.09326821526171435</v>
+        <v>-0.09319287744647871</v>
       </c>
       <c r="W100">
-        <v>0.2610724498044974</v>
+        <v>0.2610544591342192</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9391,7 +9450,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>-0.3730728610468574</v>
+        <v>-0.3727715097859148</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9402,25 +9461,25 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.3690782544586796</v>
+        <v>0.3468284863090817</v>
       </c>
       <c r="C101">
-        <v>-84.55985170457865</v>
+        <v>-90.07296869749325</v>
       </c>
       <c r="D101">
-        <v>37.90314829542136</v>
+        <v>32.48903130250674</v>
       </c>
       <c r="E101">
-        <v>122.463</v>
+        <v>122.562</v>
       </c>
       <c r="F101">
-        <v>122.463</v>
+        <v>122.562</v>
       </c>
       <c r="G101">
         <v>0</v>
       </c>
       <c r="H101">
-        <v>123.7</v>
+        <v>123.8</v>
       </c>
       <c r="I101">
         <v>0</v>
@@ -9435,37 +9494,37 @@
         <v>-10.8</v>
       </c>
       <c r="M101">
-        <v>29.2441644</v>
+        <v>29.2678056</v>
       </c>
       <c r="N101">
-        <v>-40.0441644</v>
+        <v>-40.0678056</v>
       </c>
       <c r="O101">
-        <v>-10.0110411</v>
+        <v>-10.0169514</v>
       </c>
       <c r="P101">
-        <v>-30.0331233</v>
+        <v>-30.0508542</v>
       </c>
       <c r="Q101">
-        <v>-19.2331233</v>
+        <v>-19.2508542</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>11.08392536502721</v>
+        <v>8.860711635754685</v>
       </c>
       <c r="T101">
-        <v>91.11861425341765</v>
+        <v>89.47260532209945</v>
       </c>
       <c r="U101">
         <v>0.2388</v>
       </c>
       <c r="V101">
-        <v>-0.09232611207725258</v>
+        <v>-0.09225153525004963</v>
       </c>
       <c r="W101">
-        <v>0.2608474755640479</v>
+        <v>0.2608296666177119</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9473,7 +9532,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>-0.3693044483090102</v>
+        <v>-0.3690061410001984</v>
       </c>
       <c r="Z101">
         <v>0</v>
